--- a/sitkana/Fixed Vessel Cases/Site 3 Speed/results_df.xlsx
+++ b/sitkana/Fixed Vessel Cases/Site 3 Speed/results_df.xlsx
@@ -544,7 +544,7 @@
         <v>1.639131757261307</v>
       </c>
       <c r="E2" t="n">
-        <v>119.4041845993208</v>
+        <v>119.3526953819084</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -580,13 +580,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q2" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R2" t="n">
         <v>273.04</v>
       </c>
       <c r="S2" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T2" t="n">
         <v>3000</v>
@@ -606,7 +606,7 @@
         <v>4.740417331067797</v>
       </c>
       <c r="E3" t="n">
-        <v>11.89493249995076</v>
+        <v>11.85296518872162</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -642,13 +642,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>1752.86</v>
+        <v>35.09</v>
       </c>
       <c r="R3" t="n">
         <v>663.05</v>
       </c>
       <c r="S3" t="n">
-        <v>582.83</v>
+        <v>13.09</v>
       </c>
       <c r="T3" t="n">
         <v>3000</v>
@@ -668,7 +668,7 @@
         <v>9.617118147381087</v>
       </c>
       <c r="E4" t="n">
-        <v>47.43241576791889</v>
+        <v>47.38092655050644</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -704,13 +704,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R4" t="n">
         <v>273.04</v>
       </c>
       <c r="S4" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T4" t="n">
         <v>3000</v>
@@ -730,7 +730,7 @@
         <v>4.417101358306865</v>
       </c>
       <c r="E5" t="n">
-        <v>27.92079593475058</v>
+        <v>27.87422352187419</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -766,13 +766,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q5" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R5" t="n">
         <v>457.33</v>
       </c>
       <c r="S5" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>3000</v>
@@ -792,7 +792,7 @@
         <v>13.48553865863102</v>
       </c>
       <c r="E6" t="n">
-        <v>189.504389124789</v>
+        <v>189.4724966765093</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -826,13 +826,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R6" t="n">
         <v>110.18</v>
       </c>
       <c r="S6" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T6" t="n">
         <v>3000</v>
@@ -852,7 +852,7 @@
         <v>1.092754504840872</v>
       </c>
       <c r="E7" t="n">
-        <v>119.4041845993208</v>
+        <v>119.3526953819084</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -888,13 +888,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q7" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R7" t="n">
         <v>273.04</v>
       </c>
       <c r="S7" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T7" t="n">
         <v>3000</v>
@@ -914,7 +914,7 @@
         <v>2.760007964259895</v>
       </c>
       <c r="E8" t="n">
-        <v>53.09869422366962</v>
+        <v>53.05212181079323</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -950,13 +950,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q8" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R8" t="n">
         <v>457.33</v>
       </c>
       <c r="S8" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>3000</v>
@@ -976,7 +976,7 @@
         <v>12.3365263698127</v>
       </c>
       <c r="E9" t="n">
-        <v>477.3914579038444</v>
+        <v>477.3595654555647</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -1010,13 +1010,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q9" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R9" t="n">
         <v>110.18</v>
       </c>
       <c r="S9" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T9" t="n">
         <v>3000</v>
@@ -1036,7 +1036,7 @@
         <v>9.632527613307872</v>
       </c>
       <c r="E10" t="n">
-        <v>189.504389124789</v>
+        <v>189.4724966765093</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -1070,13 +1070,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R10" t="n">
         <v>110.18</v>
       </c>
       <c r="S10" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T10" t="n">
         <v>3000</v>
@@ -1096,7 +1096,7 @@
         <v>4.917395271783922</v>
       </c>
       <c r="E11" t="n">
-        <v>119.4041845993208</v>
+        <v>119.3526953819084</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -1132,13 +1132,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q11" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R11" t="n">
         <v>273.04</v>
       </c>
       <c r="S11" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T11" t="n">
         <v>3000</v>
@@ -1158,7 +1158,7 @@
         <v>6.869370105272204</v>
       </c>
       <c r="E12" t="n">
-        <v>47.43241576791889</v>
+        <v>47.38092655050644</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1194,13 +1194,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R12" t="n">
         <v>273.04</v>
       </c>
       <c r="S12" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T12" t="n">
         <v>3000</v>
@@ -1220,7 +1220,7 @@
         <v>5.735185707448657</v>
       </c>
       <c r="E13" t="n">
-        <v>21.11124140971286</v>
+        <v>21.06466899683647</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -1256,13 +1256,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R13" t="n">
         <v>457.33</v>
       </c>
       <c r="S13" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T13" t="n">
         <v>3000</v>
@@ -1282,7 +1282,7 @@
         <v>15.78128704741558</v>
       </c>
       <c r="E14" t="n">
-        <v>250.7903784564843</v>
+        <v>250.7584860082047</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1316,13 +1316,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q14" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R14" t="n">
         <v>110.18</v>
       </c>
       <c r="S14" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T14" t="n">
         <v>3000</v>
@@ -1342,7 +1342,7 @@
         <v>2.249345149737844</v>
       </c>
       <c r="E15" t="n">
-        <v>15.72530687435428</v>
+        <v>15.68333956312514</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -1378,13 +1378,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q15" t="n">
-        <v>1752.86</v>
+        <v>35.09</v>
       </c>
       <c r="R15" t="n">
         <v>663.05</v>
       </c>
       <c r="S15" t="n">
-        <v>582.83</v>
+        <v>13.09</v>
       </c>
       <c r="T15" t="n">
         <v>3000</v>
@@ -1404,7 +1404,7 @@
         <v>8.106553014388503</v>
       </c>
       <c r="E16" t="n">
-        <v>62.7539134492536</v>
+        <v>62.70242423184115</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -1440,13 +1440,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q16" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R16" t="n">
         <v>273.04</v>
       </c>
       <c r="S16" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T16" t="n">
         <v>3000</v>
@@ -1466,7 +1466,7 @@
         <v>1.926623428612717</v>
       </c>
       <c r="E17" t="n">
-        <v>294.8679477951077</v>
+        <v>294.8153747896363</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -1502,13 +1502,13 @@
         <v>351.50272692</v>
       </c>
       <c r="Q17" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R17" t="n">
         <v>273.04</v>
       </c>
       <c r="S17" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T17" t="n">
         <v>3000</v>
@@ -1528,7 +1528,7 @@
         <v>4.131408207449998</v>
       </c>
       <c r="E18" t="n">
-        <v>1154.931784111928</v>
+        <v>1154.899891663648</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -1562,13 +1562,13 @@
         <v>351.50272692</v>
       </c>
       <c r="Q18" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R18" t="n">
         <v>110.18</v>
       </c>
       <c r="S18" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T18" t="n">
         <v>3000</v>
@@ -1588,7 +1588,7 @@
         <v>4.096561219606184</v>
       </c>
       <c r="E19" t="n">
-        <v>21.11124140971286</v>
+        <v>21.06466899683647</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -1624,13 +1624,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R19" t="n">
         <v>457.33</v>
       </c>
       <c r="S19" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T19" t="n">
         <v>3000</v>
@@ -1650,7 +1650,7 @@
         <v>8.767381693008655</v>
       </c>
       <c r="E20" t="n">
-        <v>250.7903784564843</v>
+        <v>250.7584860082047</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1684,13 +1684,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q20" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R20" t="n">
         <v>110.18</v>
       </c>
       <c r="S20" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T20" t="n">
         <v>3000</v>
@@ -1710,7 +1710,7 @@
         <v>2.741450304402821</v>
       </c>
       <c r="E21" t="n">
-        <v>477.3914579038444</v>
+        <v>477.3595654555647</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -1744,13 +1744,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q21" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R21" t="n">
         <v>110.18</v>
       </c>
       <c r="S21" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T21" t="n">
         <v>3000</v>
@@ -1770,7 +1770,7 @@
         <v>3.213317494683332</v>
       </c>
       <c r="E22" t="n">
-        <v>1154.931784111928</v>
+        <v>1154.899891663648</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -1804,13 +1804,13 @@
         <v>351.50272692</v>
       </c>
       <c r="Q22" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R22" t="n">
         <v>110.18</v>
       </c>
       <c r="S22" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T22" t="n">
         <v>3000</v>
@@ -1830,7 +1830,7 @@
         <v>0.9180907127666663</v>
       </c>
       <c r="E23" t="n">
-        <v>1154.931784111928</v>
+        <v>1154.899891663648</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -1864,13 +1864,13 @@
         <v>351.50272692</v>
       </c>
       <c r="Q23" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R23" t="n">
         <v>110.18</v>
       </c>
       <c r="S23" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T23" t="n">
         <v>3000</v>
@@ -1890,7 +1890,7 @@
         <v>1.377136069149999</v>
       </c>
       <c r="E24" t="n">
-        <v>1154.931784111928</v>
+        <v>1154.899891663648</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -1924,13 +1924,13 @@
         <v>351.50272692</v>
       </c>
       <c r="Q24" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R24" t="n">
         <v>110.18</v>
       </c>
       <c r="S24" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T24" t="n">
         <v>3000</v>
@@ -1950,7 +1950,7 @@
         <v>1.498484888921002</v>
       </c>
       <c r="E25" t="n">
-        <v>294.8679477951077</v>
+        <v>294.8153747896363</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1986,13 +1986,13 @@
         <v>351.50272692</v>
       </c>
       <c r="Q25" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R25" t="n">
         <v>273.04</v>
       </c>
       <c r="S25" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T25" t="n">
         <v>3000</v>
@@ -2012,7 +2012,7 @@
         <v>1.753476338601731</v>
       </c>
       <c r="E26" t="n">
-        <v>250.7903784564843</v>
+        <v>250.7584860082047</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -2046,13 +2046,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q26" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R26" t="n">
         <v>110.18</v>
       </c>
       <c r="S26" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T26" t="n">
         <v>3000</v>
@@ -2072,7 +2072,7 @@
         <v>4.112175456604231</v>
       </c>
       <c r="E27" t="n">
-        <v>477.3914579038444</v>
+        <v>477.3595654555647</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
@@ -2106,13 +2106,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q27" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R27" t="n">
         <v>110.18</v>
       </c>
       <c r="S27" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T27" t="n">
         <v>3000</v>
@@ -2132,7 +2132,7 @@
         <v>4.503640563549168</v>
       </c>
       <c r="E28" t="n">
-        <v>62.7539134492536</v>
+        <v>62.70242423184115</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -2168,13 +2168,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q28" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R28" t="n">
         <v>273.04</v>
       </c>
       <c r="S28" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T28" t="n">
         <v>3000</v>
@@ -2194,7 +2194,7 @@
         <v>6.305096788968836</v>
       </c>
       <c r="E29" t="n">
-        <v>62.7539134492536</v>
+        <v>62.70242423184115</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
@@ -2230,13 +2230,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q29" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R29" t="n">
         <v>273.04</v>
       </c>
       <c r="S29" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T29" t="n">
         <v>3000</v>
@@ -2256,7 +2256,7 @@
         <v>1.370725152201411</v>
       </c>
       <c r="E30" t="n">
-        <v>477.3914579038444</v>
+        <v>477.3595654555647</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -2290,13 +2290,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q30" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R30" t="n">
         <v>110.18</v>
       </c>
       <c r="S30" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T30" t="n">
         <v>3000</v>
@@ -2316,7 +2316,7 @@
         <v>2.892015192520085</v>
       </c>
       <c r="E31" t="n">
-        <v>15.72530687435428</v>
+        <v>15.68333956312514</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
@@ -2352,13 +2352,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q31" t="n">
-        <v>1752.86</v>
+        <v>35.09</v>
       </c>
       <c r="R31" t="n">
         <v>663.05</v>
       </c>
       <c r="S31" t="n">
-        <v>582.83</v>
+        <v>13.09</v>
       </c>
       <c r="T31" t="n">
         <v>3000</v>
@@ -2378,7 +2378,7 @@
         <v>1.070346349229287</v>
       </c>
       <c r="E32" t="n">
-        <v>294.8679477951077</v>
+        <v>294.8153747896363</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -2414,13 +2414,13 @@
         <v>351.50272692</v>
       </c>
       <c r="Q32" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R32" t="n">
         <v>273.04</v>
       </c>
       <c r="S32" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T32" t="n">
         <v>3000</v>
@@ -2440,7 +2440,7 @@
         <v>1.801456225419667</v>
       </c>
       <c r="E33" t="n">
-        <v>62.7539134492536</v>
+        <v>62.70242423184115</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -2476,13 +2476,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q33" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R33" t="n">
         <v>273.04</v>
       </c>
       <c r="S33" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T33" t="n">
         <v>3000</v>
@@ -2502,7 +2502,7 @@
         <v>5.260429015805194</v>
       </c>
       <c r="E34" t="n">
-        <v>250.7903784564843</v>
+        <v>250.7584860082047</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
@@ -2536,13 +2536,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q34" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R34" t="n">
         <v>110.18</v>
       </c>
       <c r="S34" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T34" t="n">
         <v>3000</v>
@@ -2562,7 +2562,7 @@
         <v>3.506952677203462</v>
       </c>
       <c r="E35" t="n">
-        <v>250.7903784564843</v>
+        <v>250.7584860082047</v>
       </c>
       <c r="F35" t="n">
         <v>1</v>
@@ -2596,13 +2596,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q35" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R35" t="n">
         <v>110.18</v>
       </c>
       <c r="S35" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T35" t="n">
         <v>3000</v>
@@ -2622,7 +2622,7 @@
         <v>2.295226781916666</v>
       </c>
       <c r="E36" t="n">
-        <v>1154.931784111928</v>
+        <v>1154.899891663648</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -2656,13 +2656,13 @@
         <v>351.50272692</v>
       </c>
       <c r="Q36" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R36" t="n">
         <v>110.18</v>
       </c>
       <c r="S36" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T36" t="n">
         <v>3000</v>
@@ -2682,7 +2682,7 @@
         <v>2.702184338129501</v>
       </c>
       <c r="E37" t="n">
-        <v>62.7539134492536</v>
+        <v>62.70242423184115</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
@@ -2718,13 +2718,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q37" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R37" t="n">
         <v>273.04</v>
       </c>
       <c r="S37" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T37" t="n">
         <v>3000</v>
@@ -2744,7 +2744,7 @@
         <v>12.27433437021212</v>
       </c>
       <c r="E38" t="n">
-        <v>250.7903784564843</v>
+        <v>250.7584860082047</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
@@ -2778,13 +2778,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q38" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R38" t="n">
         <v>110.18</v>
       </c>
       <c r="S38" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T38" t="n">
         <v>3000</v>
@@ -2804,7 +2804,7 @@
         <v>7.373810195291131</v>
       </c>
       <c r="E39" t="n">
-        <v>21.11124140971286</v>
+        <v>21.06466899683647</v>
       </c>
       <c r="F39" t="n">
         <v>1</v>
@@ -2840,13 +2840,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q39" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R39" t="n">
         <v>457.33</v>
       </c>
       <c r="S39" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T39" t="n">
         <v>3000</v>
@@ -2866,7 +2866,7 @@
         <v>1.373874021054441</v>
       </c>
       <c r="E40" t="n">
-        <v>47.43241576791889</v>
+        <v>47.38092655050644</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
@@ -2902,13 +2902,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q40" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R40" t="n">
         <v>273.04</v>
       </c>
       <c r="S40" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T40" t="n">
         <v>3000</v>
@@ -2928,7 +2928,7 @@
         <v>3.82464076694305</v>
       </c>
       <c r="E41" t="n">
-        <v>119.4041845993208</v>
+        <v>119.3526953819084</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
@@ -2964,13 +2964,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q41" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R41" t="n">
         <v>273.04</v>
       </c>
       <c r="S41" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T41" t="n">
         <v>3000</v>
@@ -2990,7 +2990,7 @@
         <v>2.633565183926554</v>
       </c>
       <c r="E42" t="n">
-        <v>11.89493249995076</v>
+        <v>11.85296518872162</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -3026,13 +3026,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q42" t="n">
-        <v>1752.86</v>
+        <v>35.09</v>
       </c>
       <c r="R42" t="n">
         <v>663.05</v>
       </c>
       <c r="S42" t="n">
-        <v>582.83</v>
+        <v>13.09</v>
       </c>
       <c r="T42" t="n">
         <v>3000</v>
@@ -3052,7 +3052,7 @@
         <v>2.453945199059369</v>
       </c>
       <c r="E43" t="n">
-        <v>27.92079593475058</v>
+        <v>27.87422352187419</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
@@ -3088,13 +3088,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q43" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R43" t="n">
         <v>457.33</v>
       </c>
       <c r="S43" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T43" t="n">
         <v>3000</v>
@@ -3114,7 +3114,7 @@
         <v>9.595076065409874</v>
       </c>
       <c r="E44" t="n">
-        <v>477.3914579038444</v>
+        <v>477.3595654555647</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
@@ -3148,13 +3148,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q44" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R44" t="n">
         <v>110.18</v>
       </c>
       <c r="S44" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T44" t="n">
         <v>3000</v>
@@ -3174,7 +3174,7 @@
         <v>1.926505522661574</v>
       </c>
       <c r="E45" t="n">
-        <v>189.504389124789</v>
+        <v>189.4724966765093</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
@@ -3208,13 +3208,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q45" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R45" t="n">
         <v>110.18</v>
       </c>
       <c r="S45" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T45" t="n">
         <v>3000</v>
@@ -3234,7 +3234,7 @@
         <v>2.146672861091029</v>
       </c>
       <c r="E46" t="n">
-        <v>53.09869422366962</v>
+        <v>53.05212181079323</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
@@ -3270,13 +3270,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q46" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R46" t="n">
         <v>457.33</v>
       </c>
       <c r="S46" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T46" t="n">
         <v>3000</v>
@@ -3296,7 +3296,7 @@
         <v>5.779516567984722</v>
       </c>
       <c r="E47" t="n">
-        <v>189.504389124789</v>
+        <v>189.4724966765093</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
@@ -3330,13 +3330,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q47" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R47" t="n">
         <v>110.18</v>
       </c>
       <c r="S47" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T47" t="n">
         <v>3000</v>
@@ -3356,7 +3356,7 @@
         <v>2.747748042108882</v>
       </c>
       <c r="E48" t="n">
-        <v>47.43241576791889</v>
+        <v>47.38092655050644</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
@@ -3392,13 +3392,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q48" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R48" t="n">
         <v>273.04</v>
       </c>
       <c r="S48" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T48" t="n">
         <v>3000</v>
@@ -3418,7 +3418,7 @@
         <v>1.533337757922164</v>
       </c>
       <c r="E49" t="n">
-        <v>53.09869422366962</v>
+        <v>53.05212181079323</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -3454,13 +3454,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q49" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R49" t="n">
         <v>457.33</v>
       </c>
       <c r="S49" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T49" t="n">
         <v>3000</v>
@@ -3480,7 +3480,7 @@
         <v>17.33854970395417</v>
       </c>
       <c r="E50" t="n">
-        <v>189.504389124789</v>
+        <v>189.4724966765093</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
@@ -3514,13 +3514,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q50" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R50" t="n">
         <v>110.18</v>
       </c>
       <c r="S50" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T50" t="n">
         <v>3000</v>
@@ -3540,7 +3540,7 @@
         <v>2.45793673176371</v>
       </c>
       <c r="E51" t="n">
-        <v>21.11124140971286</v>
+        <v>21.06466899683647</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
@@ -3576,13 +3576,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q51" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R51" t="n">
         <v>457.33</v>
       </c>
       <c r="S51" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T51" t="n">
         <v>3000</v>
@@ -3602,7 +3602,7 @@
         <v>3.435523278683117</v>
       </c>
       <c r="E52" t="n">
-        <v>27.92079593475058</v>
+        <v>27.87422352187419</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
@@ -3638,13 +3638,13 @@
         <v>2038.101387</v>
       </c>
       <c r="Q52" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R52" t="n">
         <v>457.33</v>
       </c>
       <c r="S52" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T52" t="n">
         <v>3000</v>
@@ -3664,7 +3664,7 @@
         <v>6.853625761007053</v>
       </c>
       <c r="E53" t="n">
-        <v>477.3914579038444</v>
+        <v>477.3595654555647</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
@@ -3698,13 +3698,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q53" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R53" t="n">
         <v>110.18</v>
       </c>
       <c r="S53" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T53" t="n">
         <v>3000</v>
@@ -3724,7 +3724,7 @@
         <v>12.36486618948997</v>
       </c>
       <c r="E54" t="n">
-        <v>47.43241576791889</v>
+        <v>47.38092655050644</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
@@ -3760,13 +3760,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q54" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R54" t="n">
         <v>273.04</v>
       </c>
       <c r="S54" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T54" t="n">
         <v>3000</v>
@@ -3786,7 +3786,7 @@
         <v>3.686991257497175</v>
       </c>
       <c r="E55" t="n">
-        <v>11.89493249995076</v>
+        <v>11.85296518872162</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
@@ -3822,13 +3822,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q55" t="n">
-        <v>1752.86</v>
+        <v>35.09</v>
       </c>
       <c r="R55" t="n">
         <v>663.05</v>
       </c>
       <c r="S55" t="n">
-        <v>582.83</v>
+        <v>13.09</v>
       </c>
       <c r="T55" t="n">
         <v>3000</v>
@@ -3848,7 +3848,7 @@
         <v>1.638624487842474</v>
       </c>
       <c r="E56" t="n">
-        <v>21.11124140971286</v>
+        <v>21.06466899683647</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -3884,13 +3884,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q56" t="n">
-        <v>1058.145</v>
+        <v>21.195</v>
       </c>
       <c r="R56" t="n">
         <v>457.33</v>
       </c>
       <c r="S56" t="n">
-        <v>400.7925</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="T56" t="n">
         <v>3000</v>
@@ -3910,7 +3910,7 @@
         <v>2.731886262102179</v>
       </c>
       <c r="E57" t="n">
-        <v>119.4041845993208</v>
+        <v>119.3526953819084</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -3946,13 +3946,13 @@
         <v>1145.126633</v>
       </c>
       <c r="Q57" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R57" t="n">
         <v>273.04</v>
       </c>
       <c r="S57" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T57" t="n">
         <v>3000</v>
@@ -3972,7 +3972,7 @@
         <v>4.121622063163323</v>
       </c>
       <c r="E58" t="n">
-        <v>47.43241576791889</v>
+        <v>47.38092655050644</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
@@ -4008,13 +4008,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q58" t="n">
-        <v>503.4300000000001</v>
+        <v>10.09</v>
       </c>
       <c r="R58" t="n">
         <v>273.04</v>
       </c>
       <c r="S58" t="n">
-        <v>214.85</v>
+        <v>6.56</v>
       </c>
       <c r="T58" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         <v>3.853011045323148</v>
       </c>
       <c r="E59" t="n">
-        <v>189.504389124789</v>
+        <v>189.4724966765093</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
@@ -4068,13 +4068,13 @@
         <v>3493.867132999999</v>
       </c>
       <c r="Q59" t="n">
-        <v>88.71500000000003</v>
+        <v>1.775</v>
       </c>
       <c r="R59" t="n">
         <v>110.18</v>
       </c>
       <c r="S59" t="n">
-        <v>25.00250000000003</v>
+        <v>3.295</v>
       </c>
       <c r="T59" t="n">
         <v>3000</v>
@@ -4094,7 +4094,7 @@
         <v>1.639131757261307</v>
       </c>
       <c r="E60" t="n">
-        <v>31.46437302924906</v>
+        <v>31.41288381183662</v>
       </c>
       <c r="F60" t="n">
         <v>2</v>
@@ -4130,13 +4130,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q60" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R60" t="n">
         <v>546.08</v>
       </c>
       <c r="S60" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T60" t="n">
         <v>3000</v>
@@ -4156,7 +4156,7 @@
         <v>4.740417331067797</v>
       </c>
       <c r="E61" t="n">
-        <v>5.935976498441075</v>
+        <v>5.894009187211934</v>
       </c>
       <c r="F61" t="n">
         <v>2</v>
@@ -4192,13 +4192,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q61" t="n">
-        <v>3505.72</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="R61" t="n">
         <v>1326.1</v>
       </c>
       <c r="S61" t="n">
-        <v>1165.66</v>
+        <v>26.18</v>
       </c>
       <c r="T61" t="n">
         <v>3000</v>
@@ -4218,7 +4218,7 @@
         <v>9.617118147381087</v>
       </c>
       <c r="E62" t="n">
-        <v>23.59659147606387</v>
+        <v>23.54510225865143</v>
       </c>
       <c r="F62" t="n">
         <v>2</v>
@@ -4254,13 +4254,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q62" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R62" t="n">
         <v>546.08</v>
       </c>
       <c r="S62" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T62" t="n">
         <v>3000</v>
@@ -4280,7 +4280,7 @@
         <v>4.417101358306865</v>
       </c>
       <c r="E63" t="n">
-        <v>10.621866684826</v>
+        <v>10.57529427194962</v>
       </c>
       <c r="F63" t="n">
         <v>2</v>
@@ -4316,13 +4316,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q63" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R63" t="n">
         <v>914.66</v>
       </c>
       <c r="S63" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T63" t="n">
         <v>3000</v>
@@ -4342,7 +4342,7 @@
         <v>13.48553865863102</v>
       </c>
       <c r="E64" t="n">
-        <v>94.16109412547553</v>
+        <v>94.12920167719589</v>
       </c>
       <c r="F64" t="n">
         <v>2</v>
@@ -4378,13 +4378,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q64" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R64" t="n">
         <v>220.36</v>
       </c>
       <c r="S64" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T64" t="n">
         <v>3000</v>
@@ -4404,7 +4404,7 @@
         <v>1.092754504840872</v>
       </c>
       <c r="E65" t="n">
-        <v>31.46437302924906</v>
+        <v>31.41288381183662</v>
       </c>
       <c r="F65" t="n">
         <v>2</v>
@@ -4440,13 +4440,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q65" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R65" t="n">
         <v>546.08</v>
       </c>
       <c r="S65" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T65" t="n">
         <v>3000</v>
@@ -4466,7 +4466,7 @@
         <v>2.760007964259895</v>
       </c>
       <c r="E66" t="n">
-        <v>14.01433352585953</v>
+        <v>13.96776111298314</v>
       </c>
       <c r="F66" t="n">
         <v>2</v>
@@ -4502,13 +4502,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q66" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R66" t="n">
         <v>914.66</v>
       </c>
       <c r="S66" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T66" t="n">
         <v>3000</v>
@@ -4528,7 +4528,7 @@
         <v>12.3365263698127</v>
       </c>
       <c r="E67" t="n">
-        <v>125.6322196225628</v>
+        <v>125.6003271742832</v>
       </c>
       <c r="F67" t="n">
         <v>2</v>
@@ -4564,13 +4564,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q67" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R67" t="n">
         <v>220.36</v>
       </c>
       <c r="S67" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T67" t="n">
         <v>3000</v>
@@ -4590,7 +4590,7 @@
         <v>9.632527613307872</v>
       </c>
       <c r="E68" t="n">
-        <v>94.16109412547553</v>
+        <v>94.12920167719589</v>
       </c>
       <c r="F68" t="n">
         <v>2</v>
@@ -4626,13 +4626,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q68" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R68" t="n">
         <v>220.36</v>
       </c>
       <c r="S68" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T68" t="n">
         <v>3000</v>
@@ -4652,7 +4652,7 @@
         <v>4.917395271783922</v>
       </c>
       <c r="E69" t="n">
-        <v>31.46437302924906</v>
+        <v>31.41288381183662</v>
       </c>
       <c r="F69" t="n">
         <v>2</v>
@@ -4688,13 +4688,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q69" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R69" t="n">
         <v>546.08</v>
       </c>
       <c r="S69" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T69" t="n">
         <v>3000</v>
@@ -4714,7 +4714,7 @@
         <v>6.869370105272204</v>
       </c>
       <c r="E70" t="n">
-        <v>23.59659147606387</v>
+        <v>23.54510225865143</v>
       </c>
       <c r="F70" t="n">
         <v>2</v>
@@ -4750,13 +4750,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q70" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R70" t="n">
         <v>546.08</v>
       </c>
       <c r="S70" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T70" t="n">
         <v>3000</v>
@@ -4776,7 +4776,7 @@
         <v>5.735185707448657</v>
       </c>
       <c r="E71" t="n">
-        <v>10.51754172444385</v>
+        <v>10.47096931156747</v>
       </c>
       <c r="F71" t="n">
         <v>2</v>
@@ -4812,13 +4812,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q71" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R71" t="n">
         <v>914.66</v>
       </c>
       <c r="S71" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T71" t="n">
         <v>3000</v>
@@ -4838,7 +4838,7 @@
         <v>15.78128704741558</v>
       </c>
       <c r="E72" t="n">
-        <v>95.10001874756372</v>
+        <v>95.0681262992841</v>
       </c>
       <c r="F72" t="n">
         <v>2</v>
@@ -4874,13 +4874,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q72" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R72" t="n">
         <v>220.36</v>
       </c>
       <c r="S72" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T72" t="n">
         <v>3000</v>
@@ -4900,7 +4900,7 @@
         <v>2.249345149737844</v>
       </c>
       <c r="E73" t="n">
-        <v>5.994659287952365</v>
+        <v>5.952691976723225</v>
       </c>
       <c r="F73" t="n">
         <v>2</v>
@@ -4936,13 +4936,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q73" t="n">
-        <v>3505.72</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="R73" t="n">
         <v>1326.1</v>
       </c>
       <c r="S73" t="n">
-        <v>1165.66</v>
+        <v>26.18</v>
       </c>
       <c r="T73" t="n">
         <v>3000</v>
@@ -4962,7 +4962,7 @@
         <v>8.106553014388503</v>
       </c>
       <c r="E74" t="n">
-        <v>23.83132263692371</v>
+        <v>23.77983341951126</v>
       </c>
       <c r="F74" t="n">
         <v>2</v>
@@ -4998,13 +4998,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q74" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R74" t="n">
         <v>546.08</v>
       </c>
       <c r="S74" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T74" t="n">
         <v>3000</v>
@@ -5024,7 +5024,7 @@
         <v>1.926623428612717</v>
       </c>
       <c r="E75" t="n">
-        <v>115.4116726064809</v>
+        <v>115.3590996010094</v>
       </c>
       <c r="F75" t="n">
         <v>2</v>
@@ -5060,13 +5060,13 @@
         <v>703.00545384</v>
       </c>
       <c r="Q75" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R75" t="n">
         <v>546.08</v>
       </c>
       <c r="S75" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T75" t="n">
         <v>3000</v>
@@ -5086,7 +5086,7 @@
         <v>4.131408207449998</v>
       </c>
       <c r="E76" t="n">
-        <v>451.9046030536584</v>
+        <v>451.8727106053788</v>
       </c>
       <c r="F76" t="n">
         <v>2</v>
@@ -5122,13 +5122,13 @@
         <v>703.00545384</v>
       </c>
       <c r="Q76" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R76" t="n">
         <v>220.36</v>
       </c>
       <c r="S76" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T76" t="n">
         <v>3000</v>
@@ -5148,7 +5148,7 @@
         <v>4.096561219606184</v>
       </c>
       <c r="E77" t="n">
-        <v>10.51754172444385</v>
+        <v>10.47096931156747</v>
       </c>
       <c r="F77" t="n">
         <v>2</v>
@@ -5184,13 +5184,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q77" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R77" t="n">
         <v>914.66</v>
       </c>
       <c r="S77" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T77" t="n">
         <v>3000</v>
@@ -5210,7 +5210,7 @@
         <v>8.767381693008655</v>
       </c>
       <c r="E78" t="n">
-        <v>95.10001874756372</v>
+        <v>95.0681262992841</v>
       </c>
       <c r="F78" t="n">
         <v>2</v>
@@ -5246,13 +5246,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q78" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R78" t="n">
         <v>220.36</v>
       </c>
       <c r="S78" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T78" t="n">
         <v>3000</v>
@@ -5272,7 +5272,7 @@
         <v>2.741450304402821</v>
       </c>
       <c r="E79" t="n">
-        <v>125.6322196225628</v>
+        <v>125.6003271742832</v>
       </c>
       <c r="F79" t="n">
         <v>2</v>
@@ -5308,13 +5308,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q79" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R79" t="n">
         <v>220.36</v>
       </c>
       <c r="S79" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T79" t="n">
         <v>3000</v>
@@ -5334,7 +5334,7 @@
         <v>3.213317494683332</v>
       </c>
       <c r="E80" t="n">
-        <v>451.9046030536584</v>
+        <v>451.8727106053788</v>
       </c>
       <c r="F80" t="n">
         <v>2</v>
@@ -5370,13 +5370,13 @@
         <v>703.00545384</v>
       </c>
       <c r="Q80" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R80" t="n">
         <v>220.36</v>
       </c>
       <c r="S80" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T80" t="n">
         <v>3000</v>
@@ -5396,7 +5396,7 @@
         <v>0.9180907127666663</v>
       </c>
       <c r="E81" t="n">
-        <v>451.9046030536584</v>
+        <v>451.8727106053788</v>
       </c>
       <c r="F81" t="n">
         <v>2</v>
@@ -5432,13 +5432,13 @@
         <v>703.00545384</v>
       </c>
       <c r="Q81" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R81" t="n">
         <v>220.36</v>
       </c>
       <c r="S81" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T81" t="n">
         <v>3000</v>
@@ -5458,7 +5458,7 @@
         <v>1.377136069149999</v>
       </c>
       <c r="E82" t="n">
-        <v>451.9046030536584</v>
+        <v>451.8727106053788</v>
       </c>
       <c r="F82" t="n">
         <v>2</v>
@@ -5494,13 +5494,13 @@
         <v>703.00545384</v>
       </c>
       <c r="Q82" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R82" t="n">
         <v>220.36</v>
       </c>
       <c r="S82" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T82" t="n">
         <v>3000</v>
@@ -5520,7 +5520,7 @@
         <v>1.498484888921002</v>
       </c>
       <c r="E83" t="n">
-        <v>115.4116726064809</v>
+        <v>115.3590996010094</v>
       </c>
       <c r="F83" t="n">
         <v>2</v>
@@ -5556,13 +5556,13 @@
         <v>703.00545384</v>
       </c>
       <c r="Q83" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R83" t="n">
         <v>546.08</v>
       </c>
       <c r="S83" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T83" t="n">
         <v>3000</v>
@@ -5582,7 +5582,7 @@
         <v>1.753476338601731</v>
       </c>
       <c r="E84" t="n">
-        <v>95.10001874756372</v>
+        <v>95.0681262992841</v>
       </c>
       <c r="F84" t="n">
         <v>2</v>
@@ -5618,13 +5618,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q84" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R84" t="n">
         <v>220.36</v>
       </c>
       <c r="S84" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T84" t="n">
         <v>3000</v>
@@ -5644,7 +5644,7 @@
         <v>4.112175456604231</v>
       </c>
       <c r="E85" t="n">
-        <v>125.6322196225628</v>
+        <v>125.6003271742832</v>
       </c>
       <c r="F85" t="n">
         <v>2</v>
@@ -5680,13 +5680,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q85" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R85" t="n">
         <v>220.36</v>
       </c>
       <c r="S85" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T85" t="n">
         <v>3000</v>
@@ -5706,7 +5706,7 @@
         <v>4.503640563549168</v>
       </c>
       <c r="E86" t="n">
-        <v>23.83132263692371</v>
+        <v>23.77983341951126</v>
       </c>
       <c r="F86" t="n">
         <v>2</v>
@@ -5742,13 +5742,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q86" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R86" t="n">
         <v>546.08</v>
       </c>
       <c r="S86" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T86" t="n">
         <v>3000</v>
@@ -5768,7 +5768,7 @@
         <v>6.305096788968836</v>
       </c>
       <c r="E87" t="n">
-        <v>23.83132263692371</v>
+        <v>23.77983341951126</v>
       </c>
       <c r="F87" t="n">
         <v>2</v>
@@ -5804,13 +5804,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q87" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R87" t="n">
         <v>546.08</v>
       </c>
       <c r="S87" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T87" t="n">
         <v>3000</v>
@@ -5830,7 +5830,7 @@
         <v>1.370725152201411</v>
       </c>
       <c r="E88" t="n">
-        <v>125.6322196225628</v>
+        <v>125.6003271742832</v>
       </c>
       <c r="F88" t="n">
         <v>2</v>
@@ -5866,13 +5866,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q88" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R88" t="n">
         <v>220.36</v>
       </c>
       <c r="S88" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T88" t="n">
         <v>3000</v>
@@ -5892,7 +5892,7 @@
         <v>2.892015192520085</v>
       </c>
       <c r="E89" t="n">
-        <v>5.994659287952365</v>
+        <v>5.952691976723225</v>
       </c>
       <c r="F89" t="n">
         <v>2</v>
@@ -5928,13 +5928,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q89" t="n">
-        <v>3505.72</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="R89" t="n">
         <v>1326.1</v>
       </c>
       <c r="S89" t="n">
-        <v>1165.66</v>
+        <v>26.18</v>
       </c>
       <c r="T89" t="n">
         <v>3000</v>
@@ -5954,7 +5954,7 @@
         <v>1.070346349229287</v>
       </c>
       <c r="E90" t="n">
-        <v>115.4116726064809</v>
+        <v>115.3590996010094</v>
       </c>
       <c r="F90" t="n">
         <v>2</v>
@@ -5990,13 +5990,13 @@
         <v>703.00545384</v>
       </c>
       <c r="Q90" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R90" t="n">
         <v>546.08</v>
       </c>
       <c r="S90" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T90" t="n">
         <v>3000</v>
@@ -6016,7 +6016,7 @@
         <v>1.801456225419667</v>
       </c>
       <c r="E91" t="n">
-        <v>23.83132263692371</v>
+        <v>23.77983341951126</v>
       </c>
       <c r="F91" t="n">
         <v>2</v>
@@ -6052,13 +6052,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q91" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R91" t="n">
         <v>546.08</v>
       </c>
       <c r="S91" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T91" t="n">
         <v>3000</v>
@@ -6078,7 +6078,7 @@
         <v>5.260429015805194</v>
       </c>
       <c r="E92" t="n">
-        <v>95.10001874756372</v>
+        <v>95.0681262992841</v>
       </c>
       <c r="F92" t="n">
         <v>2</v>
@@ -6114,13 +6114,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q92" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R92" t="n">
         <v>220.36</v>
       </c>
       <c r="S92" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T92" t="n">
         <v>3000</v>
@@ -6140,7 +6140,7 @@
         <v>3.506952677203462</v>
       </c>
       <c r="E93" t="n">
-        <v>95.10001874756372</v>
+        <v>95.0681262992841</v>
       </c>
       <c r="F93" t="n">
         <v>2</v>
@@ -6176,13 +6176,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q93" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R93" t="n">
         <v>220.36</v>
       </c>
       <c r="S93" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T93" t="n">
         <v>3000</v>
@@ -6202,7 +6202,7 @@
         <v>2.295226781916666</v>
       </c>
       <c r="E94" t="n">
-        <v>451.9046030536584</v>
+        <v>451.8727106053788</v>
       </c>
       <c r="F94" t="n">
         <v>2</v>
@@ -6238,13 +6238,13 @@
         <v>703.00545384</v>
       </c>
       <c r="Q94" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R94" t="n">
         <v>220.36</v>
       </c>
       <c r="S94" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T94" t="n">
         <v>3000</v>
@@ -6264,7 +6264,7 @@
         <v>2.702184338129501</v>
       </c>
       <c r="E95" t="n">
-        <v>23.83132263692371</v>
+        <v>23.77983341951126</v>
       </c>
       <c r="F95" t="n">
         <v>2</v>
@@ -6300,13 +6300,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q95" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R95" t="n">
         <v>546.08</v>
       </c>
       <c r="S95" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T95" t="n">
         <v>3000</v>
@@ -6326,7 +6326,7 @@
         <v>12.27433437021212</v>
       </c>
       <c r="E96" t="n">
-        <v>95.10001874756372</v>
+        <v>95.0681262992841</v>
       </c>
       <c r="F96" t="n">
         <v>2</v>
@@ -6362,13 +6362,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q96" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R96" t="n">
         <v>220.36</v>
       </c>
       <c r="S96" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T96" t="n">
         <v>3000</v>
@@ -6388,7 +6388,7 @@
         <v>7.373810195291131</v>
       </c>
       <c r="E97" t="n">
-        <v>10.51754172444385</v>
+        <v>10.47096931156747</v>
       </c>
       <c r="F97" t="n">
         <v>2</v>
@@ -6424,13 +6424,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q97" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R97" t="n">
         <v>914.66</v>
       </c>
       <c r="S97" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T97" t="n">
         <v>3000</v>
@@ -6450,7 +6450,7 @@
         <v>1.373874021054441</v>
       </c>
       <c r="E98" t="n">
-        <v>23.59659147606387</v>
+        <v>23.54510225865143</v>
       </c>
       <c r="F98" t="n">
         <v>2</v>
@@ -6486,13 +6486,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q98" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R98" t="n">
         <v>546.08</v>
       </c>
       <c r="S98" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T98" t="n">
         <v>3000</v>
@@ -6512,7 +6512,7 @@
         <v>3.82464076694305</v>
       </c>
       <c r="E99" t="n">
-        <v>31.46437302924906</v>
+        <v>31.41288381183662</v>
       </c>
       <c r="F99" t="n">
         <v>2</v>
@@ -6548,13 +6548,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q99" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R99" t="n">
         <v>546.08</v>
       </c>
       <c r="S99" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T99" t="n">
         <v>3000</v>
@@ -6574,7 +6574,7 @@
         <v>2.633565183926554</v>
       </c>
       <c r="E100" t="n">
-        <v>5.935976498441075</v>
+        <v>5.894009187211934</v>
       </c>
       <c r="F100" t="n">
         <v>2</v>
@@ -6610,13 +6610,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q100" t="n">
-        <v>3505.72</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="R100" t="n">
         <v>1326.1</v>
       </c>
       <c r="S100" t="n">
-        <v>1165.66</v>
+        <v>26.18</v>
       </c>
       <c r="T100" t="n">
         <v>3000</v>
@@ -6636,7 +6636,7 @@
         <v>2.453945199059369</v>
       </c>
       <c r="E101" t="n">
-        <v>10.621866684826</v>
+        <v>10.57529427194962</v>
       </c>
       <c r="F101" t="n">
         <v>2</v>
@@ -6672,13 +6672,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q101" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R101" t="n">
         <v>914.66</v>
       </c>
       <c r="S101" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T101" t="n">
         <v>3000</v>
@@ -6698,7 +6698,7 @@
         <v>9.595076065409874</v>
       </c>
       <c r="E102" t="n">
-        <v>125.6322196225628</v>
+        <v>125.6003271742832</v>
       </c>
       <c r="F102" t="n">
         <v>2</v>
@@ -6734,13 +6734,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q102" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R102" t="n">
         <v>220.36</v>
       </c>
       <c r="S102" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T102" t="n">
         <v>3000</v>
@@ -6760,7 +6760,7 @@
         <v>1.926505522661574</v>
       </c>
       <c r="E103" t="n">
-        <v>94.16109412547553</v>
+        <v>94.12920167719589</v>
       </c>
       <c r="F103" t="n">
         <v>2</v>
@@ -6796,13 +6796,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q103" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R103" t="n">
         <v>220.36</v>
       </c>
       <c r="S103" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T103" t="n">
         <v>3000</v>
@@ -6822,7 +6822,7 @@
         <v>2.146672861091029</v>
       </c>
       <c r="E104" t="n">
-        <v>14.01433352585953</v>
+        <v>13.96776111298314</v>
       </c>
       <c r="F104" t="n">
         <v>2</v>
@@ -6858,13 +6858,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q104" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R104" t="n">
         <v>914.66</v>
       </c>
       <c r="S104" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T104" t="n">
         <v>3000</v>
@@ -6884,7 +6884,7 @@
         <v>5.779516567984722</v>
       </c>
       <c r="E105" t="n">
-        <v>94.16109412547553</v>
+        <v>94.12920167719589</v>
       </c>
       <c r="F105" t="n">
         <v>2</v>
@@ -6920,13 +6920,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q105" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R105" t="n">
         <v>220.36</v>
       </c>
       <c r="S105" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T105" t="n">
         <v>3000</v>
@@ -6946,7 +6946,7 @@
         <v>2.747748042108882</v>
       </c>
       <c r="E106" t="n">
-        <v>23.59659147606387</v>
+        <v>23.54510225865143</v>
       </c>
       <c r="F106" t="n">
         <v>2</v>
@@ -6982,13 +6982,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q106" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R106" t="n">
         <v>546.08</v>
       </c>
       <c r="S106" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T106" t="n">
         <v>3000</v>
@@ -7008,7 +7008,7 @@
         <v>1.533337757922164</v>
       </c>
       <c r="E107" t="n">
-        <v>14.01433352585953</v>
+        <v>13.96776111298314</v>
       </c>
       <c r="F107" t="n">
         <v>2</v>
@@ -7044,13 +7044,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q107" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R107" t="n">
         <v>914.66</v>
       </c>
       <c r="S107" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T107" t="n">
         <v>3000</v>
@@ -7070,7 +7070,7 @@
         <v>17.33854970395417</v>
       </c>
       <c r="E108" t="n">
-        <v>94.16109412547553</v>
+        <v>94.12920167719589</v>
       </c>
       <c r="F108" t="n">
         <v>2</v>
@@ -7106,13 +7106,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q108" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R108" t="n">
         <v>220.36</v>
       </c>
       <c r="S108" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T108" t="n">
         <v>3000</v>
@@ -7132,7 +7132,7 @@
         <v>2.45793673176371</v>
       </c>
       <c r="E109" t="n">
-        <v>10.51754172444385</v>
+        <v>10.47096931156747</v>
       </c>
       <c r="F109" t="n">
         <v>2</v>
@@ -7168,13 +7168,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q109" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R109" t="n">
         <v>914.66</v>
       </c>
       <c r="S109" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T109" t="n">
         <v>3000</v>
@@ -7194,7 +7194,7 @@
         <v>3.435523278683117</v>
       </c>
       <c r="E110" t="n">
-        <v>10.621866684826</v>
+        <v>10.57529427194962</v>
       </c>
       <c r="F110" t="n">
         <v>2</v>
@@ -7230,13 +7230,13 @@
         <v>4076.202774</v>
       </c>
       <c r="Q110" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R110" t="n">
         <v>914.66</v>
       </c>
       <c r="S110" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T110" t="n">
         <v>3000</v>
@@ -7256,7 +7256,7 @@
         <v>6.853625761007053</v>
       </c>
       <c r="E111" t="n">
-        <v>125.6322196225628</v>
+        <v>125.6003271742832</v>
       </c>
       <c r="F111" t="n">
         <v>2</v>
@@ -7292,13 +7292,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q111" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R111" t="n">
         <v>220.36</v>
       </c>
       <c r="S111" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T111" t="n">
         <v>3000</v>
@@ -7318,7 +7318,7 @@
         <v>12.36486618948997</v>
       </c>
       <c r="E112" t="n">
-        <v>23.59659147606387</v>
+        <v>23.54510225865143</v>
       </c>
       <c r="F112" t="n">
         <v>2</v>
@@ -7354,13 +7354,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q112" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R112" t="n">
         <v>546.08</v>
       </c>
       <c r="S112" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T112" t="n">
         <v>3000</v>
@@ -7380,7 +7380,7 @@
         <v>3.686991257497175</v>
       </c>
       <c r="E113" t="n">
-        <v>5.935976498441075</v>
+        <v>5.894009187211934</v>
       </c>
       <c r="F113" t="n">
         <v>2</v>
@@ -7416,13 +7416,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q113" t="n">
-        <v>3505.72</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="R113" t="n">
         <v>1326.1</v>
       </c>
       <c r="S113" t="n">
-        <v>1165.66</v>
+        <v>26.18</v>
       </c>
       <c r="T113" t="n">
         <v>3000</v>
@@ -7442,7 +7442,7 @@
         <v>1.638624487842474</v>
       </c>
       <c r="E114" t="n">
-        <v>10.51754172444385</v>
+        <v>10.47096931156747</v>
       </c>
       <c r="F114" t="n">
         <v>2</v>
@@ -7478,13 +7478,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q114" t="n">
-        <v>2116.29</v>
+        <v>42.39</v>
       </c>
       <c r="R114" t="n">
         <v>914.66</v>
       </c>
       <c r="S114" t="n">
-        <v>801.585</v>
+        <v>19.65</v>
       </c>
       <c r="T114" t="n">
         <v>3000</v>
@@ -7504,7 +7504,7 @@
         <v>2.731886262102179</v>
       </c>
       <c r="E115" t="n">
-        <v>31.46437302924906</v>
+        <v>31.41288381183662</v>
       </c>
       <c r="F115" t="n">
         <v>2</v>
@@ -7540,13 +7540,13 @@
         <v>2290.253266</v>
       </c>
       <c r="Q115" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R115" t="n">
         <v>546.08</v>
       </c>
       <c r="S115" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T115" t="n">
         <v>3000</v>
@@ -7566,7 +7566,7 @@
         <v>4.121622063163323</v>
       </c>
       <c r="E116" t="n">
-        <v>23.59659147606387</v>
+        <v>23.54510225865143</v>
       </c>
       <c r="F116" t="n">
         <v>2</v>
@@ -7602,13 +7602,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q116" t="n">
-        <v>1006.86</v>
+        <v>20.18</v>
       </c>
       <c r="R116" t="n">
         <v>546.08</v>
       </c>
       <c r="S116" t="n">
-        <v>429.7</v>
+        <v>13.12</v>
       </c>
       <c r="T116" t="n">
         <v>3000</v>
@@ -7628,7 +7628,7 @@
         <v>3.853011045323148</v>
       </c>
       <c r="E117" t="n">
-        <v>94.16109412547553</v>
+        <v>94.12920167719589</v>
       </c>
       <c r="F117" t="n">
         <v>2</v>
@@ -7664,13 +7664,13 @@
         <v>6987.734265999999</v>
       </c>
       <c r="Q117" t="n">
-        <v>177.4300000000001</v>
+        <v>3.550000000000001</v>
       </c>
       <c r="R117" t="n">
         <v>220.36</v>
       </c>
       <c r="S117" t="n">
-        <v>50.00500000000005</v>
+        <v>6.59</v>
       </c>
       <c r="T117" t="n">
         <v>3000</v>
@@ -7690,7 +7690,7 @@
         <v>1.639131757261307</v>
       </c>
       <c r="E118" t="n">
-        <v>12.00307762308412</v>
+        <v>11.95158840567167</v>
       </c>
       <c r="F118" t="n">
         <v>4</v>
@@ -7726,13 +7726,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q118" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R118" t="n">
         <v>1092.16</v>
       </c>
       <c r="S118" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T118" t="n">
         <v>3000</v>
@@ -7752,7 +7752,7 @@
         <v>9.617118147381087</v>
       </c>
       <c r="E119" t="n">
-        <v>12.08301712008756</v>
+        <v>12.03152790267512</v>
       </c>
       <c r="F119" t="n">
         <v>4</v>
@@ -7788,13 +7788,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q119" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R119" t="n">
         <v>1092.16</v>
       </c>
       <c r="S119" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T119" t="n">
         <v>3000</v>
@@ -7814,7 +7814,7 @@
         <v>4.417101358306865</v>
       </c>
       <c r="E120" t="n">
-        <v>5.325016842191498</v>
+        <v>5.27844442931511</v>
       </c>
       <c r="F120" t="n">
         <v>4</v>
@@ -7850,13 +7850,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q120" t="n">
-        <v>4232.58</v>
+        <v>84.78</v>
       </c>
       <c r="R120" t="n">
         <v>1829.32</v>
       </c>
       <c r="S120" t="n">
-        <v>1603.17</v>
+        <v>39.3</v>
       </c>
       <c r="T120" t="n">
         <v>3000</v>
@@ -7876,7 +7876,7 @@
         <v>13.48553865863102</v>
       </c>
       <c r="E121" t="n">
-        <v>48.10679774884505</v>
+        <v>48.07490530056543</v>
       </c>
       <c r="F121" t="n">
         <v>4</v>
@@ -7912,13 +7912,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q121" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R121" t="n">
         <v>440.72</v>
       </c>
       <c r="S121" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T121" t="n">
         <v>3000</v>
@@ -7938,7 +7938,7 @@
         <v>1.092754504840872</v>
       </c>
       <c r="E122" t="n">
-        <v>12.00307762308412</v>
+        <v>11.95158840567167</v>
       </c>
       <c r="F122" t="n">
         <v>4</v>
@@ -7974,13 +7974,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q122" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R122" t="n">
         <v>1092.16</v>
       </c>
       <c r="S122" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T122" t="n">
         <v>3000</v>
@@ -8000,7 +8000,7 @@
         <v>2.760007964259895</v>
       </c>
       <c r="E123" t="n">
-        <v>5.36486890089724</v>
+        <v>5.318296488020853</v>
       </c>
       <c r="F123" t="n">
         <v>4</v>
@@ -8036,13 +8036,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q123" t="n">
-        <v>4232.58</v>
+        <v>84.78</v>
       </c>
       <c r="R123" t="n">
         <v>1829.32</v>
       </c>
       <c r="S123" t="n">
-        <v>1603.17</v>
+        <v>39.3</v>
       </c>
       <c r="T123" t="n">
         <v>3000</v>
@@ -8062,7 +8062,7 @@
         <v>12.3365263698127</v>
       </c>
       <c r="E124" t="n">
-        <v>47.78703976810257</v>
+        <v>47.75514731982295</v>
       </c>
       <c r="F124" t="n">
         <v>4</v>
@@ -8098,13 +8098,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q124" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R124" t="n">
         <v>440.72</v>
       </c>
       <c r="S124" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T124" t="n">
         <v>3000</v>
@@ -8124,7 +8124,7 @@
         <v>9.632527613307872</v>
       </c>
       <c r="E125" t="n">
-        <v>48.10679774884505</v>
+        <v>48.07490530056543</v>
       </c>
       <c r="F125" t="n">
         <v>4</v>
@@ -8160,13 +8160,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q125" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R125" t="n">
         <v>440.72</v>
       </c>
       <c r="S125" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T125" t="n">
         <v>3000</v>
@@ -8186,7 +8186,7 @@
         <v>4.917395271783922</v>
       </c>
       <c r="E126" t="n">
-        <v>12.00307762308412</v>
+        <v>11.95158840567167</v>
       </c>
       <c r="F126" t="n">
         <v>4</v>
@@ -8222,13 +8222,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q126" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R126" t="n">
         <v>1092.16</v>
       </c>
       <c r="S126" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T126" t="n">
         <v>3000</v>
@@ -8248,7 +8248,7 @@
         <v>6.869370105272204</v>
       </c>
       <c r="E127" t="n">
-        <v>12.08301712008756</v>
+        <v>12.03152790267512</v>
       </c>
       <c r="F127" t="n">
         <v>4</v>
@@ -8284,13 +8284,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q127" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R127" t="n">
         <v>1092.16</v>
       </c>
       <c r="S127" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T127" t="n">
         <v>3000</v>
@@ -8310,7 +8310,7 @@
         <v>15.78128704741558</v>
       </c>
       <c r="E128" t="n">
-        <v>47.42837124790701</v>
+        <v>47.39647879962739</v>
       </c>
       <c r="F128" t="n">
         <v>4</v>
@@ -8346,13 +8346,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q128" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R128" t="n">
         <v>440.72</v>
       </c>
       <c r="S128" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T128" t="n">
         <v>3000</v>
@@ -8372,7 +8372,7 @@
         <v>8.106553014388503</v>
       </c>
       <c r="E129" t="n">
-        <v>11.9134104909962</v>
+        <v>11.86192127358375</v>
       </c>
       <c r="F129" t="n">
         <v>4</v>
@@ -8408,13 +8408,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q129" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R129" t="n">
         <v>1092.16</v>
       </c>
       <c r="S129" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T129" t="n">
         <v>3000</v>
@@ -8434,7 +8434,7 @@
         <v>1.926623428612717</v>
       </c>
       <c r="E130" t="n">
-        <v>37.08462396094477</v>
+        <v>37.03205095547328</v>
       </c>
       <c r="F130" t="n">
         <v>4</v>
@@ -8470,13 +8470,13 @@
         <v>1406.01090768</v>
       </c>
       <c r="Q130" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R130" t="n">
         <v>1092.16</v>
       </c>
       <c r="S130" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T130" t="n">
         <v>3000</v>
@@ -8496,7 +8496,7 @@
         <v>4.131408207449998</v>
       </c>
       <c r="E131" t="n">
-        <v>145.0552373683113</v>
+        <v>145.0233449200317</v>
       </c>
       <c r="F131" t="n">
         <v>4</v>
@@ -8532,13 +8532,13 @@
         <v>1406.01090768</v>
       </c>
       <c r="Q131" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R131" t="n">
         <v>440.72</v>
       </c>
       <c r="S131" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T131" t="n">
         <v>3000</v>
@@ -8558,7 +8558,7 @@
         <v>4.096561219606184</v>
       </c>
       <c r="E132" t="n">
-        <v>5.400397566232105</v>
+        <v>5.353825153355718</v>
       </c>
       <c r="F132" t="n">
         <v>4</v>
@@ -8594,13 +8594,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q132" t="n">
-        <v>4232.58</v>
+        <v>84.78</v>
       </c>
       <c r="R132" t="n">
         <v>1829.32</v>
       </c>
       <c r="S132" t="n">
-        <v>1603.17</v>
+        <v>39.3</v>
       </c>
       <c r="T132" t="n">
         <v>3000</v>
@@ -8620,7 +8620,7 @@
         <v>8.767381693008655</v>
       </c>
       <c r="E133" t="n">
-        <v>47.42837124790701</v>
+        <v>47.39647879962739</v>
       </c>
       <c r="F133" t="n">
         <v>4</v>
@@ -8656,13 +8656,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q133" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R133" t="n">
         <v>440.72</v>
       </c>
       <c r="S133" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T133" t="n">
         <v>3000</v>
@@ -8682,7 +8682,7 @@
         <v>2.741450304402821</v>
       </c>
       <c r="E134" t="n">
-        <v>47.78703976810257</v>
+        <v>47.75514731982295</v>
       </c>
       <c r="F134" t="n">
         <v>4</v>
@@ -8718,13 +8718,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q134" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R134" t="n">
         <v>440.72</v>
       </c>
       <c r="S134" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T134" t="n">
         <v>3000</v>
@@ -8744,7 +8744,7 @@
         <v>3.213317494683332</v>
       </c>
       <c r="E135" t="n">
-        <v>145.0552373683113</v>
+        <v>145.0233449200317</v>
       </c>
       <c r="F135" t="n">
         <v>4</v>
@@ -8780,13 +8780,13 @@
         <v>1406.01090768</v>
       </c>
       <c r="Q135" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R135" t="n">
         <v>440.72</v>
       </c>
       <c r="S135" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T135" t="n">
         <v>3000</v>
@@ -8806,7 +8806,7 @@
         <v>0.9180907127666663</v>
       </c>
       <c r="E136" t="n">
-        <v>145.0552373683113</v>
+        <v>145.0233449200317</v>
       </c>
       <c r="F136" t="n">
         <v>4</v>
@@ -8842,13 +8842,13 @@
         <v>1406.01090768</v>
       </c>
       <c r="Q136" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R136" t="n">
         <v>440.72</v>
       </c>
       <c r="S136" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T136" t="n">
         <v>3000</v>
@@ -8868,7 +8868,7 @@
         <v>1.377136069149999</v>
       </c>
       <c r="E137" t="n">
-        <v>145.0552373683113</v>
+        <v>145.0233449200317</v>
       </c>
       <c r="F137" t="n">
         <v>4</v>
@@ -8904,13 +8904,13 @@
         <v>1406.01090768</v>
       </c>
       <c r="Q137" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R137" t="n">
         <v>440.72</v>
       </c>
       <c r="S137" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T137" t="n">
         <v>3000</v>
@@ -8930,7 +8930,7 @@
         <v>1.498484888921002</v>
       </c>
       <c r="E138" t="n">
-        <v>37.08462396094477</v>
+        <v>37.03205095547328</v>
       </c>
       <c r="F138" t="n">
         <v>4</v>
@@ -8966,13 +8966,13 @@
         <v>1406.01090768</v>
       </c>
       <c r="Q138" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R138" t="n">
         <v>1092.16</v>
       </c>
       <c r="S138" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T138" t="n">
         <v>3000</v>
@@ -8992,7 +8992,7 @@
         <v>1.753476338601731</v>
       </c>
       <c r="E139" t="n">
-        <v>47.42837124790701</v>
+        <v>47.39647879962739</v>
       </c>
       <c r="F139" t="n">
         <v>4</v>
@@ -9028,13 +9028,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q139" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R139" t="n">
         <v>440.72</v>
       </c>
       <c r="S139" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T139" t="n">
         <v>3000</v>
@@ -9054,7 +9054,7 @@
         <v>4.112175456604231</v>
       </c>
       <c r="E140" t="n">
-        <v>47.78703976810257</v>
+        <v>47.75514731982295</v>
       </c>
       <c r="F140" t="n">
         <v>4</v>
@@ -9090,13 +9090,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q140" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R140" t="n">
         <v>440.72</v>
       </c>
       <c r="S140" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T140" t="n">
         <v>3000</v>
@@ -9116,7 +9116,7 @@
         <v>4.503640563549168</v>
       </c>
       <c r="E141" t="n">
-        <v>11.9134104909962</v>
+        <v>11.86192127358375</v>
       </c>
       <c r="F141" t="n">
         <v>4</v>
@@ -9152,13 +9152,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q141" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R141" t="n">
         <v>1092.16</v>
       </c>
       <c r="S141" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T141" t="n">
         <v>3000</v>
@@ -9178,7 +9178,7 @@
         <v>6.305096788968836</v>
       </c>
       <c r="E142" t="n">
-        <v>11.9134104909962</v>
+        <v>11.86192127358375</v>
       </c>
       <c r="F142" t="n">
         <v>4</v>
@@ -9214,13 +9214,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q142" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R142" t="n">
         <v>1092.16</v>
       </c>
       <c r="S142" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T142" t="n">
         <v>3000</v>
@@ -9240,7 +9240,7 @@
         <v>1.370725152201411</v>
       </c>
       <c r="E143" t="n">
-        <v>47.78703976810257</v>
+        <v>47.75514731982295</v>
       </c>
       <c r="F143" t="n">
         <v>4</v>
@@ -9276,13 +9276,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q143" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R143" t="n">
         <v>440.72</v>
       </c>
       <c r="S143" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T143" t="n">
         <v>3000</v>
@@ -9302,7 +9302,7 @@
         <v>1.070346349229287</v>
       </c>
       <c r="E144" t="n">
-        <v>37.08462396094477</v>
+        <v>37.03205095547328</v>
       </c>
       <c r="F144" t="n">
         <v>4</v>
@@ -9338,13 +9338,13 @@
         <v>1406.01090768</v>
       </c>
       <c r="Q144" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R144" t="n">
         <v>1092.16</v>
       </c>
       <c r="S144" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T144" t="n">
         <v>3000</v>
@@ -9364,7 +9364,7 @@
         <v>1.801456225419667</v>
       </c>
       <c r="E145" t="n">
-        <v>11.9134104909962</v>
+        <v>11.86192127358375</v>
       </c>
       <c r="F145" t="n">
         <v>4</v>
@@ -9400,13 +9400,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q145" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R145" t="n">
         <v>1092.16</v>
       </c>
       <c r="S145" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T145" t="n">
         <v>3000</v>
@@ -9426,7 +9426,7 @@
         <v>5.260429015805194</v>
       </c>
       <c r="E146" t="n">
-        <v>47.42837124790701</v>
+        <v>47.39647879962739</v>
       </c>
       <c r="F146" t="n">
         <v>4</v>
@@ -9462,13 +9462,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q146" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R146" t="n">
         <v>440.72</v>
       </c>
       <c r="S146" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T146" t="n">
         <v>3000</v>
@@ -9488,7 +9488,7 @@
         <v>3.506952677203462</v>
       </c>
       <c r="E147" t="n">
-        <v>47.42837124790701</v>
+        <v>47.39647879962739</v>
       </c>
       <c r="F147" t="n">
         <v>4</v>
@@ -9524,13 +9524,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q147" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R147" t="n">
         <v>440.72</v>
       </c>
       <c r="S147" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T147" t="n">
         <v>3000</v>
@@ -9550,7 +9550,7 @@
         <v>2.295226781916666</v>
       </c>
       <c r="E148" t="n">
-        <v>145.0552373683113</v>
+        <v>145.0233449200317</v>
       </c>
       <c r="F148" t="n">
         <v>4</v>
@@ -9586,13 +9586,13 @@
         <v>1406.01090768</v>
       </c>
       <c r="Q148" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R148" t="n">
         <v>440.72</v>
       </c>
       <c r="S148" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T148" t="n">
         <v>3000</v>
@@ -9612,7 +9612,7 @@
         <v>2.702184338129501</v>
       </c>
       <c r="E149" t="n">
-        <v>11.9134104909962</v>
+        <v>11.86192127358375</v>
       </c>
       <c r="F149" t="n">
         <v>4</v>
@@ -9648,13 +9648,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q149" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R149" t="n">
         <v>1092.16</v>
       </c>
       <c r="S149" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T149" t="n">
         <v>3000</v>
@@ -9674,7 +9674,7 @@
         <v>12.27433437021212</v>
       </c>
       <c r="E150" t="n">
-        <v>47.42837124790701</v>
+        <v>47.39647879962739</v>
       </c>
       <c r="F150" t="n">
         <v>4</v>
@@ -9710,13 +9710,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q150" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R150" t="n">
         <v>440.72</v>
       </c>
       <c r="S150" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T150" t="n">
         <v>3000</v>
@@ -9736,7 +9736,7 @@
         <v>1.373874021054441</v>
       </c>
       <c r="E151" t="n">
-        <v>12.08301712008756</v>
+        <v>12.03152790267512</v>
       </c>
       <c r="F151" t="n">
         <v>4</v>
@@ -9772,13 +9772,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q151" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R151" t="n">
         <v>1092.16</v>
       </c>
       <c r="S151" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T151" t="n">
         <v>3000</v>
@@ -9798,7 +9798,7 @@
         <v>3.82464076694305</v>
       </c>
       <c r="E152" t="n">
-        <v>12.00307762308412</v>
+        <v>11.95158840567167</v>
       </c>
       <c r="F152" t="n">
         <v>4</v>
@@ -9834,13 +9834,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q152" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R152" t="n">
         <v>1092.16</v>
       </c>
       <c r="S152" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T152" t="n">
         <v>3000</v>
@@ -9860,7 +9860,7 @@
         <v>2.453945199059369</v>
       </c>
       <c r="E153" t="n">
-        <v>5.325016842191498</v>
+        <v>5.27844442931511</v>
       </c>
       <c r="F153" t="n">
         <v>4</v>
@@ -9896,13 +9896,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q153" t="n">
-        <v>4232.58</v>
+        <v>84.78</v>
       </c>
       <c r="R153" t="n">
         <v>1829.32</v>
       </c>
       <c r="S153" t="n">
-        <v>1603.17</v>
+        <v>39.3</v>
       </c>
       <c r="T153" t="n">
         <v>3000</v>
@@ -9922,7 +9922,7 @@
         <v>9.595076065409874</v>
       </c>
       <c r="E154" t="n">
-        <v>47.78703976810257</v>
+        <v>47.75514731982295</v>
       </c>
       <c r="F154" t="n">
         <v>4</v>
@@ -9958,13 +9958,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q154" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R154" t="n">
         <v>440.72</v>
       </c>
       <c r="S154" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T154" t="n">
         <v>3000</v>
@@ -9984,7 +9984,7 @@
         <v>1.926505522661574</v>
       </c>
       <c r="E155" t="n">
-        <v>48.10679774884505</v>
+        <v>48.07490530056543</v>
       </c>
       <c r="F155" t="n">
         <v>4</v>
@@ -10020,13 +10020,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q155" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R155" t="n">
         <v>440.72</v>
       </c>
       <c r="S155" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T155" t="n">
         <v>3000</v>
@@ -10046,7 +10046,7 @@
         <v>2.146672861091029</v>
       </c>
       <c r="E156" t="n">
-        <v>5.36486890089724</v>
+        <v>5.318296488020853</v>
       </c>
       <c r="F156" t="n">
         <v>4</v>
@@ -10082,13 +10082,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q156" t="n">
-        <v>4232.58</v>
+        <v>84.78</v>
       </c>
       <c r="R156" t="n">
         <v>1829.32</v>
       </c>
       <c r="S156" t="n">
-        <v>1603.17</v>
+        <v>39.3</v>
       </c>
       <c r="T156" t="n">
         <v>3000</v>
@@ -10108,7 +10108,7 @@
         <v>5.779516567984722</v>
       </c>
       <c r="E157" t="n">
-        <v>48.10679774884505</v>
+        <v>48.07490530056543</v>
       </c>
       <c r="F157" t="n">
         <v>4</v>
@@ -10144,13 +10144,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q157" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R157" t="n">
         <v>440.72</v>
       </c>
       <c r="S157" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T157" t="n">
         <v>3000</v>
@@ -10170,7 +10170,7 @@
         <v>2.747748042108882</v>
       </c>
       <c r="E158" t="n">
-        <v>12.08301712008756</v>
+        <v>12.03152790267512</v>
       </c>
       <c r="F158" t="n">
         <v>4</v>
@@ -10206,13 +10206,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q158" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R158" t="n">
         <v>1092.16</v>
       </c>
       <c r="S158" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T158" t="n">
         <v>3000</v>
@@ -10232,7 +10232,7 @@
         <v>1.533337757922164</v>
       </c>
       <c r="E159" t="n">
-        <v>5.36486890089724</v>
+        <v>5.318296488020853</v>
       </c>
       <c r="F159" t="n">
         <v>4</v>
@@ -10268,13 +10268,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q159" t="n">
-        <v>4232.58</v>
+        <v>84.78</v>
       </c>
       <c r="R159" t="n">
         <v>1829.32</v>
       </c>
       <c r="S159" t="n">
-        <v>1603.17</v>
+        <v>39.3</v>
       </c>
       <c r="T159" t="n">
         <v>3000</v>
@@ -10294,7 +10294,7 @@
         <v>17.33854970395417</v>
       </c>
       <c r="E160" t="n">
-        <v>48.10679774884505</v>
+        <v>48.07490530056543</v>
       </c>
       <c r="F160" t="n">
         <v>4</v>
@@ -10330,13 +10330,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q160" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R160" t="n">
         <v>440.72</v>
       </c>
       <c r="S160" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T160" t="n">
         <v>3000</v>
@@ -10356,7 +10356,7 @@
         <v>2.45793673176371</v>
       </c>
       <c r="E161" t="n">
-        <v>5.400397566232105</v>
+        <v>5.353825153355718</v>
       </c>
       <c r="F161" t="n">
         <v>4</v>
@@ -10392,13 +10392,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q161" t="n">
-        <v>4232.58</v>
+        <v>84.78</v>
       </c>
       <c r="R161" t="n">
         <v>1829.32</v>
       </c>
       <c r="S161" t="n">
-        <v>1603.17</v>
+        <v>39.3</v>
       </c>
       <c r="T161" t="n">
         <v>3000</v>
@@ -10418,7 +10418,7 @@
         <v>3.435523278683117</v>
       </c>
       <c r="E162" t="n">
-        <v>5.325016842191498</v>
+        <v>5.27844442931511</v>
       </c>
       <c r="F162" t="n">
         <v>4</v>
@@ -10454,13 +10454,13 @@
         <v>8152.405548</v>
       </c>
       <c r="Q162" t="n">
-        <v>4232.58</v>
+        <v>84.78</v>
       </c>
       <c r="R162" t="n">
         <v>1829.32</v>
       </c>
       <c r="S162" t="n">
-        <v>1603.17</v>
+        <v>39.3</v>
       </c>
       <c r="T162" t="n">
         <v>3000</v>
@@ -10480,7 +10480,7 @@
         <v>6.853625761007053</v>
       </c>
       <c r="E163" t="n">
-        <v>47.78703976810257</v>
+        <v>47.75514731982295</v>
       </c>
       <c r="F163" t="n">
         <v>4</v>
@@ -10516,13 +10516,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q163" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R163" t="n">
         <v>440.72</v>
       </c>
       <c r="S163" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T163" t="n">
         <v>3000</v>
@@ -10542,7 +10542,7 @@
         <v>12.36486618948997</v>
       </c>
       <c r="E164" t="n">
-        <v>12.08301712008756</v>
+        <v>12.03152790267512</v>
       </c>
       <c r="F164" t="n">
         <v>4</v>
@@ -10578,13 +10578,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q164" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R164" t="n">
         <v>1092.16</v>
       </c>
       <c r="S164" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T164" t="n">
         <v>3000</v>
@@ -10604,7 +10604,7 @@
         <v>1.638624487842474</v>
       </c>
       <c r="E165" t="n">
-        <v>5.400397566232105</v>
+        <v>5.353825153355718</v>
       </c>
       <c r="F165" t="n">
         <v>4</v>
@@ -10640,13 +10640,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q165" t="n">
-        <v>4232.58</v>
+        <v>84.78</v>
       </c>
       <c r="R165" t="n">
         <v>1829.32</v>
       </c>
       <c r="S165" t="n">
-        <v>1603.17</v>
+        <v>39.3</v>
       </c>
       <c r="T165" t="n">
         <v>3000</v>
@@ -10666,7 +10666,7 @@
         <v>2.731886262102179</v>
       </c>
       <c r="E166" t="n">
-        <v>12.00307762308412</v>
+        <v>11.95158840567167</v>
       </c>
       <c r="F166" t="n">
         <v>4</v>
@@ -10702,13 +10702,13 @@
         <v>4580.506531999999</v>
       </c>
       <c r="Q166" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R166" t="n">
         <v>1092.16</v>
       </c>
       <c r="S166" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T166" t="n">
         <v>3000</v>
@@ -10728,7 +10728,7 @@
         <v>4.121622063163323</v>
       </c>
       <c r="E167" t="n">
-        <v>12.08301712008756</v>
+        <v>12.03152790267512</v>
       </c>
       <c r="F167" t="n">
         <v>4</v>
@@ -10764,13 +10764,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q167" t="n">
-        <v>2013.72</v>
+        <v>40.36</v>
       </c>
       <c r="R167" t="n">
         <v>1092.16</v>
       </c>
       <c r="S167" t="n">
-        <v>859.4000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="T167" t="n">
         <v>3000</v>
@@ -10790,7 +10790,7 @@
         <v>3.853011045323148</v>
       </c>
       <c r="E168" t="n">
-        <v>48.10679774884505</v>
+        <v>48.07490530056543</v>
       </c>
       <c r="F168" t="n">
         <v>4</v>
@@ -10826,13 +10826,13 @@
         <v>13975.468532</v>
       </c>
       <c r="Q168" t="n">
-        <v>354.8600000000001</v>
+        <v>7.100000000000001</v>
       </c>
       <c r="R168" t="n">
         <v>440.72</v>
       </c>
       <c r="S168" t="n">
-        <v>100.0100000000001</v>
+        <v>13.18</v>
       </c>
       <c r="T168" t="n">
         <v>3000</v>
@@ -10852,7 +10852,7 @@
         <v>1.639131757261307</v>
       </c>
       <c r="E169" t="n">
-        <v>7.969366753053822</v>
+        <v>7.917877535641378</v>
       </c>
       <c r="F169" t="n">
         <v>6</v>
@@ -10888,13 +10888,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q169" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R169" t="n">
         <v>1638.24</v>
       </c>
       <c r="S169" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T169" t="n">
         <v>3000</v>
@@ -10914,7 +10914,7 @@
         <v>9.617118147381087</v>
       </c>
       <c r="E170" t="n">
-        <v>8.245494328502266</v>
+        <v>8.194005111089824</v>
       </c>
       <c r="F170" t="n">
         <v>6</v>
@@ -10950,13 +10950,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q170" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R170" t="n">
         <v>1638.24</v>
       </c>
       <c r="S170" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T170" t="n">
         <v>3000</v>
@@ -10976,7 +10976,7 @@
         <v>13.48553865863102</v>
       </c>
       <c r="E171" t="n">
-        <v>32.75670693156497</v>
+        <v>32.72481448328536</v>
       </c>
       <c r="F171" t="n">
         <v>6</v>
@@ -11012,13 +11012,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q171" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R171" t="n">
         <v>661.08</v>
       </c>
       <c r="S171" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T171" t="n">
         <v>3000</v>
@@ -11038,7 +11038,7 @@
         <v>1.092754504840872</v>
       </c>
       <c r="E172" t="n">
-        <v>7.969366753053822</v>
+        <v>7.917877535641378</v>
       </c>
       <c r="F172" t="n">
         <v>6</v>
@@ -11074,13 +11074,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q172" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R172" t="n">
         <v>1638.24</v>
       </c>
       <c r="S172" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T172" t="n">
         <v>3000</v>
@@ -11100,7 +11100,7 @@
         <v>12.3365263698127</v>
       </c>
       <c r="E173" t="n">
-        <v>31.65219665488775</v>
+        <v>31.62030420660813</v>
       </c>
       <c r="F173" t="n">
         <v>6</v>
@@ -11136,13 +11136,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q173" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R173" t="n">
         <v>661.08</v>
       </c>
       <c r="S173" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T173" t="n">
         <v>3000</v>
@@ -11162,7 +11162,7 @@
         <v>9.632527613307872</v>
       </c>
       <c r="E174" t="n">
-        <v>32.75670693156497</v>
+        <v>32.72481448328536</v>
       </c>
       <c r="F174" t="n">
         <v>6</v>
@@ -11198,13 +11198,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q174" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R174" t="n">
         <v>661.08</v>
       </c>
       <c r="S174" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T174" t="n">
         <v>3000</v>
@@ -11224,7 +11224,7 @@
         <v>4.917395271783922</v>
       </c>
       <c r="E175" t="n">
-        <v>7.969366753053822</v>
+        <v>7.917877535641378</v>
       </c>
       <c r="F175" t="n">
         <v>6</v>
@@ -11260,13 +11260,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q175" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R175" t="n">
         <v>1638.24</v>
       </c>
       <c r="S175" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T175" t="n">
         <v>3000</v>
@@ -11286,7 +11286,7 @@
         <v>6.869370105272204</v>
       </c>
       <c r="E176" t="n">
-        <v>8.245494328502266</v>
+        <v>8.194005111089824</v>
       </c>
       <c r="F176" t="n">
         <v>6</v>
@@ -11322,13 +11322,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q176" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R176" t="n">
         <v>1638.24</v>
       </c>
       <c r="S176" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T176" t="n">
         <v>3000</v>
@@ -11348,7 +11348,7 @@
         <v>15.78128704741558</v>
       </c>
       <c r="E177" t="n">
-        <v>32.07627178068142</v>
+        <v>32.0443793324018</v>
       </c>
       <c r="F177" t="n">
         <v>6</v>
@@ -11384,13 +11384,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q177" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R177" t="n">
         <v>661.08</v>
       </c>
       <c r="S177" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T177" t="n">
         <v>3000</v>
@@ -11410,7 +11410,7 @@
         <v>8.106553014388503</v>
       </c>
       <c r="E178" t="n">
-        <v>8.075385536913105</v>
+        <v>8.023896319500661</v>
       </c>
       <c r="F178" t="n">
         <v>6</v>
@@ -11446,13 +11446,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q178" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R178" t="n">
         <v>1638.24</v>
       </c>
       <c r="S178" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T178" t="n">
         <v>3000</v>
@@ -11472,7 +11472,7 @@
         <v>1.926623428612717</v>
       </c>
       <c r="E179" t="n">
-        <v>17.20138165244549</v>
+        <v>17.148808646974</v>
       </c>
       <c r="F179" t="n">
         <v>6</v>
@@ -11508,13 +11508,13 @@
         <v>2109.01636152</v>
       </c>
       <c r="Q179" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R179" t="n">
         <v>1638.24</v>
       </c>
       <c r="S179" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T179" t="n">
         <v>3000</v>
@@ -11534,7 +11534,7 @@
         <v>4.131408207449998</v>
       </c>
       <c r="E180" t="n">
-        <v>67.16183533625653</v>
+        <v>67.12994288797691</v>
       </c>
       <c r="F180" t="n">
         <v>6</v>
@@ -11570,13 +11570,13 @@
         <v>2109.01636152</v>
       </c>
       <c r="Q180" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R180" t="n">
         <v>661.08</v>
       </c>
       <c r="S180" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T180" t="n">
         <v>3000</v>
@@ -11596,7 +11596,7 @@
         <v>8.767381693008655</v>
       </c>
       <c r="E181" t="n">
-        <v>32.07627178068142</v>
+        <v>32.0443793324018</v>
       </c>
       <c r="F181" t="n">
         <v>6</v>
@@ -11632,13 +11632,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q181" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R181" t="n">
         <v>661.08</v>
       </c>
       <c r="S181" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T181" t="n">
         <v>3000</v>
@@ -11658,7 +11658,7 @@
         <v>2.741450304402821</v>
       </c>
       <c r="E182" t="n">
-        <v>31.65219665488775</v>
+        <v>31.62030420660813</v>
       </c>
       <c r="F182" t="n">
         <v>6</v>
@@ -11694,13 +11694,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q182" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R182" t="n">
         <v>661.08</v>
       </c>
       <c r="S182" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T182" t="n">
         <v>3000</v>
@@ -11720,7 +11720,7 @@
         <v>3.213317494683332</v>
       </c>
       <c r="E183" t="n">
-        <v>67.16183533625653</v>
+        <v>67.12994288797691</v>
       </c>
       <c r="F183" t="n">
         <v>6</v>
@@ -11756,13 +11756,13 @@
         <v>2109.01636152</v>
       </c>
       <c r="Q183" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R183" t="n">
         <v>661.08</v>
       </c>
       <c r="S183" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T183" t="n">
         <v>3000</v>
@@ -11782,7 +11782,7 @@
         <v>0.9180907127666663</v>
       </c>
       <c r="E184" t="n">
-        <v>67.16183533625653</v>
+        <v>67.12994288797691</v>
       </c>
       <c r="F184" t="n">
         <v>6</v>
@@ -11818,13 +11818,13 @@
         <v>2109.01636152</v>
       </c>
       <c r="Q184" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R184" t="n">
         <v>661.08</v>
       </c>
       <c r="S184" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T184" t="n">
         <v>3000</v>
@@ -11844,7 +11844,7 @@
         <v>1.377136069149999</v>
       </c>
       <c r="E185" t="n">
-        <v>67.16183533625653</v>
+        <v>67.12994288797691</v>
       </c>
       <c r="F185" t="n">
         <v>6</v>
@@ -11880,13 +11880,13 @@
         <v>2109.01636152</v>
       </c>
       <c r="Q185" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R185" t="n">
         <v>661.08</v>
       </c>
       <c r="S185" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T185" t="n">
         <v>3000</v>
@@ -11906,7 +11906,7 @@
         <v>1.498484888921002</v>
       </c>
       <c r="E186" t="n">
-        <v>17.20138165244549</v>
+        <v>17.148808646974</v>
       </c>
       <c r="F186" t="n">
         <v>6</v>
@@ -11942,13 +11942,13 @@
         <v>2109.01636152</v>
       </c>
       <c r="Q186" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R186" t="n">
         <v>1638.24</v>
       </c>
       <c r="S186" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T186" t="n">
         <v>3000</v>
@@ -11968,7 +11968,7 @@
         <v>1.753476338601731</v>
       </c>
       <c r="E187" t="n">
-        <v>32.07627178068142</v>
+        <v>32.0443793324018</v>
       </c>
       <c r="F187" t="n">
         <v>6</v>
@@ -12004,13 +12004,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q187" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R187" t="n">
         <v>661.08</v>
       </c>
       <c r="S187" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T187" t="n">
         <v>3000</v>
@@ -12030,7 +12030,7 @@
         <v>4.112175456604231</v>
       </c>
       <c r="E188" t="n">
-        <v>31.65219665488775</v>
+        <v>31.62030420660813</v>
       </c>
       <c r="F188" t="n">
         <v>6</v>
@@ -12066,13 +12066,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q188" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R188" t="n">
         <v>661.08</v>
       </c>
       <c r="S188" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T188" t="n">
         <v>3000</v>
@@ -12092,7 +12092,7 @@
         <v>4.503640563549168</v>
       </c>
       <c r="E189" t="n">
-        <v>8.075385536913105</v>
+        <v>8.023896319500661</v>
       </c>
       <c r="F189" t="n">
         <v>6</v>
@@ -12128,13 +12128,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q189" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R189" t="n">
         <v>1638.24</v>
       </c>
       <c r="S189" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T189" t="n">
         <v>3000</v>
@@ -12154,7 +12154,7 @@
         <v>6.305096788968836</v>
       </c>
       <c r="E190" t="n">
-        <v>8.075385536913105</v>
+        <v>8.023896319500661</v>
       </c>
       <c r="F190" t="n">
         <v>6</v>
@@ -12190,13 +12190,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q190" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R190" t="n">
         <v>1638.24</v>
       </c>
       <c r="S190" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T190" t="n">
         <v>3000</v>
@@ -12216,7 +12216,7 @@
         <v>1.370725152201411</v>
       </c>
       <c r="E191" t="n">
-        <v>31.65219665488775</v>
+        <v>31.62030420660813</v>
       </c>
       <c r="F191" t="n">
         <v>6</v>
@@ -12252,13 +12252,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q191" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R191" t="n">
         <v>661.08</v>
       </c>
       <c r="S191" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T191" t="n">
         <v>3000</v>
@@ -12278,7 +12278,7 @@
         <v>1.070346349229287</v>
       </c>
       <c r="E192" t="n">
-        <v>17.20138165244549</v>
+        <v>17.148808646974</v>
       </c>
       <c r="F192" t="n">
         <v>6</v>
@@ -12314,13 +12314,13 @@
         <v>2109.01636152</v>
       </c>
       <c r="Q192" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R192" t="n">
         <v>1638.24</v>
       </c>
       <c r="S192" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T192" t="n">
         <v>3000</v>
@@ -12340,7 +12340,7 @@
         <v>1.801456225419667</v>
       </c>
       <c r="E193" t="n">
-        <v>8.075385536913105</v>
+        <v>8.023896319500661</v>
       </c>
       <c r="F193" t="n">
         <v>6</v>
@@ -12376,13 +12376,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q193" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R193" t="n">
         <v>1638.24</v>
       </c>
       <c r="S193" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T193" t="n">
         <v>3000</v>
@@ -12402,7 +12402,7 @@
         <v>5.260429015805194</v>
       </c>
       <c r="E194" t="n">
-        <v>32.07627178068142</v>
+        <v>32.0443793324018</v>
       </c>
       <c r="F194" t="n">
         <v>6</v>
@@ -12438,13 +12438,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q194" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R194" t="n">
         <v>661.08</v>
       </c>
       <c r="S194" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T194" t="n">
         <v>3000</v>
@@ -12464,7 +12464,7 @@
         <v>3.506952677203462</v>
       </c>
       <c r="E195" t="n">
-        <v>32.07627178068142</v>
+        <v>32.0443793324018</v>
       </c>
       <c r="F195" t="n">
         <v>6</v>
@@ -12500,13 +12500,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q195" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R195" t="n">
         <v>661.08</v>
       </c>
       <c r="S195" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T195" t="n">
         <v>3000</v>
@@ -12526,7 +12526,7 @@
         <v>2.295226781916666</v>
       </c>
       <c r="E196" t="n">
-        <v>67.16183533625653</v>
+        <v>67.12994288797691</v>
       </c>
       <c r="F196" t="n">
         <v>6</v>
@@ -12562,13 +12562,13 @@
         <v>2109.01636152</v>
       </c>
       <c r="Q196" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R196" t="n">
         <v>661.08</v>
       </c>
       <c r="S196" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T196" t="n">
         <v>3000</v>
@@ -12588,7 +12588,7 @@
         <v>2.702184338129501</v>
       </c>
       <c r="E197" t="n">
-        <v>8.075385536913105</v>
+        <v>8.023896319500661</v>
       </c>
       <c r="F197" t="n">
         <v>6</v>
@@ -12624,13 +12624,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q197" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R197" t="n">
         <v>1638.24</v>
       </c>
       <c r="S197" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T197" t="n">
         <v>3000</v>
@@ -12650,7 +12650,7 @@
         <v>12.27433437021212</v>
       </c>
       <c r="E198" t="n">
-        <v>32.07627178068142</v>
+        <v>32.0443793324018</v>
       </c>
       <c r="F198" t="n">
         <v>6</v>
@@ -12686,13 +12686,13 @@
         <v>12228.608322</v>
       </c>
       <c r="Q198" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R198" t="n">
         <v>661.08</v>
       </c>
       <c r="S198" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T198" t="n">
         <v>3000</v>
@@ -12712,7 +12712,7 @@
         <v>1.373874021054441</v>
       </c>
       <c r="E199" t="n">
-        <v>8.245494328502266</v>
+        <v>8.194005111089824</v>
       </c>
       <c r="F199" t="n">
         <v>6</v>
@@ -12748,13 +12748,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q199" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R199" t="n">
         <v>1638.24</v>
       </c>
       <c r="S199" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T199" t="n">
         <v>3000</v>
@@ -12774,7 +12774,7 @@
         <v>3.82464076694305</v>
       </c>
       <c r="E200" t="n">
-        <v>7.969366753053822</v>
+        <v>7.917877535641378</v>
       </c>
       <c r="F200" t="n">
         <v>6</v>
@@ -12810,13 +12810,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q200" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R200" t="n">
         <v>1638.24</v>
       </c>
       <c r="S200" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T200" t="n">
         <v>3000</v>
@@ -12836,7 +12836,7 @@
         <v>9.595076065409874</v>
       </c>
       <c r="E201" t="n">
-        <v>31.65219665488775</v>
+        <v>31.62030420660813</v>
       </c>
       <c r="F201" t="n">
         <v>6</v>
@@ -12872,13 +12872,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q201" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R201" t="n">
         <v>661.08</v>
       </c>
       <c r="S201" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T201" t="n">
         <v>3000</v>
@@ -12898,7 +12898,7 @@
         <v>1.926505522661574</v>
       </c>
       <c r="E202" t="n">
-        <v>32.75670693156497</v>
+        <v>32.72481448328536</v>
       </c>
       <c r="F202" t="n">
         <v>6</v>
@@ -12934,13 +12934,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q202" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R202" t="n">
         <v>661.08</v>
       </c>
       <c r="S202" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T202" t="n">
         <v>3000</v>
@@ -12960,7 +12960,7 @@
         <v>5.779516567984722</v>
       </c>
       <c r="E203" t="n">
-        <v>32.75670693156497</v>
+        <v>32.72481448328536</v>
       </c>
       <c r="F203" t="n">
         <v>6</v>
@@ -12996,13 +12996,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q203" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R203" t="n">
         <v>661.08</v>
       </c>
       <c r="S203" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T203" t="n">
         <v>3000</v>
@@ -13022,7 +13022,7 @@
         <v>2.747748042108882</v>
       </c>
       <c r="E204" t="n">
-        <v>8.245494328502266</v>
+        <v>8.194005111089824</v>
       </c>
       <c r="F204" t="n">
         <v>6</v>
@@ -13058,13 +13058,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q204" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R204" t="n">
         <v>1638.24</v>
       </c>
       <c r="S204" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T204" t="n">
         <v>3000</v>
@@ -13084,7 +13084,7 @@
         <v>1.533337757922164</v>
       </c>
       <c r="E205" t="n">
-        <v>3.57210851421709</v>
+        <v>3.525536101340704</v>
       </c>
       <c r="F205" t="n">
         <v>6</v>
@@ -13120,13 +13120,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q205" t="n">
-        <v>6348.87</v>
+        <v>127.17</v>
       </c>
       <c r="R205" t="n">
         <v>2743.98</v>
       </c>
       <c r="S205" t="n">
-        <v>2404.755</v>
+        <v>58.95</v>
       </c>
       <c r="T205" t="n">
         <v>3000</v>
@@ -13146,7 +13146,7 @@
         <v>17.33854970395417</v>
       </c>
       <c r="E206" t="n">
-        <v>32.75670693156497</v>
+        <v>32.72481448328536</v>
       </c>
       <c r="F206" t="n">
         <v>6</v>
@@ -13182,13 +13182,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q206" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R206" t="n">
         <v>661.08</v>
       </c>
       <c r="S206" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T206" t="n">
         <v>3000</v>
@@ -13208,7 +13208,7 @@
         <v>6.853625761007053</v>
       </c>
       <c r="E207" t="n">
-        <v>31.65219665488775</v>
+        <v>31.62030420660813</v>
       </c>
       <c r="F207" t="n">
         <v>6</v>
@@ -13244,13 +13244,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q207" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R207" t="n">
         <v>661.08</v>
       </c>
       <c r="S207" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T207" t="n">
         <v>3000</v>
@@ -13270,7 +13270,7 @@
         <v>1.638624487842474</v>
       </c>
       <c r="E208" t="n">
-        <v>3.694831881083068</v>
+        <v>3.648259468206681</v>
       </c>
       <c r="F208" t="n">
         <v>6</v>
@@ -13306,13 +13306,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q208" t="n">
-        <v>6348.87</v>
+        <v>127.17</v>
       </c>
       <c r="R208" t="n">
         <v>2743.98</v>
       </c>
       <c r="S208" t="n">
-        <v>2404.755</v>
+        <v>58.95</v>
       </c>
       <c r="T208" t="n">
         <v>3000</v>
@@ -13332,7 +13332,7 @@
         <v>2.731886262102179</v>
       </c>
       <c r="E209" t="n">
-        <v>7.969366753053822</v>
+        <v>7.917877535641378</v>
       </c>
       <c r="F209" t="n">
         <v>6</v>
@@ -13368,13 +13368,13 @@
         <v>6870.759797999999</v>
       </c>
       <c r="Q209" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R209" t="n">
         <v>1638.24</v>
       </c>
       <c r="S209" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T209" t="n">
         <v>3000</v>
@@ -13394,7 +13394,7 @@
         <v>4.121622063163323</v>
       </c>
       <c r="E210" t="n">
-        <v>8.245494328502266</v>
+        <v>8.194005111089824</v>
       </c>
       <c r="F210" t="n">
         <v>6</v>
@@ -13430,13 +13430,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q210" t="n">
-        <v>3020.58</v>
+        <v>60.54</v>
       </c>
       <c r="R210" t="n">
         <v>1638.24</v>
       </c>
       <c r="S210" t="n">
-        <v>1289.1</v>
+        <v>39.36</v>
       </c>
       <c r="T210" t="n">
         <v>3000</v>
@@ -13456,7 +13456,7 @@
         <v>3.853011045323148</v>
       </c>
       <c r="E211" t="n">
-        <v>32.75670693156497</v>
+        <v>32.72481448328536</v>
       </c>
       <c r="F211" t="n">
         <v>6</v>
@@ -13492,13 +13492,13 @@
         <v>20963.20279799999</v>
       </c>
       <c r="Q211" t="n">
-        <v>532.2900000000002</v>
+        <v>10.65</v>
       </c>
       <c r="R211" t="n">
         <v>661.08</v>
       </c>
       <c r="S211" t="n">
-        <v>150.0150000000002</v>
+        <v>19.77</v>
       </c>
       <c r="T211" t="n">
         <v>3000</v>
@@ -13518,7 +13518,7 @@
         <v>1.639131757261307</v>
       </c>
       <c r="E212" t="n">
-        <v>6.04412155012036</v>
+        <v>5.992632332707918</v>
       </c>
       <c r="F212" t="n">
         <v>8</v>
@@ -13554,13 +13554,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q212" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R212" t="n">
         <v>2184.32</v>
       </c>
       <c r="S212" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T212" t="n">
         <v>3000</v>
@@ -13580,7 +13580,7 @@
         <v>13.48553865863102</v>
       </c>
       <c r="E213" t="n">
-        <v>25.08166152910587</v>
+        <v>25.04976908082626</v>
       </c>
       <c r="F213" t="n">
         <v>8</v>
@@ -13616,13 +13616,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q213" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R213" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S213" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T213" t="n">
         <v>3000</v>
@@ -13642,7 +13642,7 @@
         <v>1.092754504840872</v>
       </c>
       <c r="E214" t="n">
-        <v>6.04412155012036</v>
+        <v>5.992632332707918</v>
       </c>
       <c r="F214" t="n">
         <v>8</v>
@@ -13678,13 +13678,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q214" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R214" t="n">
         <v>2184.32</v>
       </c>
       <c r="S214" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T214" t="n">
         <v>3000</v>
@@ -13704,7 +13704,7 @@
         <v>12.3365263698127</v>
       </c>
       <c r="E215" t="n">
-        <v>23.95121601827421</v>
+        <v>23.91932356999459</v>
       </c>
       <c r="F215" t="n">
         <v>8</v>
@@ -13740,13 +13740,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q215" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R215" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S215" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T215" t="n">
         <v>3000</v>
@@ -13766,7 +13766,7 @@
         <v>9.632527613307872</v>
       </c>
       <c r="E216" t="n">
-        <v>25.08166152910587</v>
+        <v>25.04976908082626</v>
       </c>
       <c r="F216" t="n">
         <v>8</v>
@@ -13802,13 +13802,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q216" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R216" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S216" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T216" t="n">
         <v>3000</v>
@@ -13828,7 +13828,7 @@
         <v>4.917395271783922</v>
       </c>
       <c r="E217" t="n">
-        <v>6.04412155012036</v>
+        <v>5.992632332707918</v>
       </c>
       <c r="F217" t="n">
         <v>8</v>
@@ -13864,13 +13864,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q217" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R217" t="n">
         <v>2184.32</v>
       </c>
       <c r="S217" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T217" t="n">
         <v>3000</v>
@@ -13890,7 +13890,7 @@
         <v>15.78128704741558</v>
       </c>
       <c r="E218" t="n">
-        <v>24.40122305959177</v>
+        <v>24.36933061131215</v>
       </c>
       <c r="F218" t="n">
         <v>8</v>
@@ -13926,13 +13926,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q218" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R218" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S218" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T218" t="n">
         <v>3000</v>
@@ -13952,7 +13952,7 @@
         <v>1.926623428612717</v>
       </c>
       <c r="E219" t="n">
-        <v>9.822343370953043</v>
+        <v>9.769770365481554</v>
       </c>
       <c r="F219" t="n">
         <v>8</v>
@@ -13988,13 +13988,13 @@
         <v>2812.02181536</v>
       </c>
       <c r="Q219" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R219" t="n">
         <v>2184.32</v>
       </c>
       <c r="S219" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T219" t="n">
         <v>3000</v>
@@ -14014,7 +14014,7 @@
         <v>4.131408207449998</v>
       </c>
       <c r="E220" t="n">
-        <v>38.25415586667022</v>
+        <v>38.2222634183906</v>
       </c>
       <c r="F220" t="n">
         <v>8</v>
@@ -14050,13 +14050,13 @@
         <v>2812.02181536</v>
       </c>
       <c r="Q220" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R220" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S220" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T220" t="n">
         <v>3000</v>
@@ -14076,7 +14076,7 @@
         <v>8.767381693008655</v>
       </c>
       <c r="E221" t="n">
-        <v>24.40122305959177</v>
+        <v>24.36933061131215</v>
       </c>
       <c r="F221" t="n">
         <v>8</v>
@@ -14112,13 +14112,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q221" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R221" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S221" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T221" t="n">
         <v>3000</v>
@@ -14138,7 +14138,7 @@
         <v>2.741450304402821</v>
       </c>
       <c r="E222" t="n">
-        <v>23.95121601827421</v>
+        <v>23.91932356999459</v>
       </c>
       <c r="F222" t="n">
         <v>8</v>
@@ -14174,13 +14174,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q222" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R222" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S222" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T222" t="n">
         <v>3000</v>
@@ -14200,7 +14200,7 @@
         <v>3.213317494683332</v>
       </c>
       <c r="E223" t="n">
-        <v>38.25415586667022</v>
+        <v>38.2222634183906</v>
       </c>
       <c r="F223" t="n">
         <v>8</v>
@@ -14236,13 +14236,13 @@
         <v>2812.02181536</v>
       </c>
       <c r="Q223" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R223" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S223" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T223" t="n">
         <v>3000</v>
@@ -14262,7 +14262,7 @@
         <v>0.9180907127666663</v>
       </c>
       <c r="E224" t="n">
-        <v>38.25415586667022</v>
+        <v>38.2222634183906</v>
       </c>
       <c r="F224" t="n">
         <v>8</v>
@@ -14298,13 +14298,13 @@
         <v>2812.02181536</v>
       </c>
       <c r="Q224" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R224" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S224" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T224" t="n">
         <v>3000</v>
@@ -14324,7 +14324,7 @@
         <v>1.377136069149999</v>
       </c>
       <c r="E225" t="n">
-        <v>38.25415586667022</v>
+        <v>38.2222634183906</v>
       </c>
       <c r="F225" t="n">
         <v>8</v>
@@ -14360,13 +14360,13 @@
         <v>2812.02181536</v>
       </c>
       <c r="Q225" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R225" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S225" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T225" t="n">
         <v>3000</v>
@@ -14386,7 +14386,7 @@
         <v>1.498484888921002</v>
       </c>
       <c r="E226" t="n">
-        <v>9.822343370953043</v>
+        <v>9.769770365481554</v>
       </c>
       <c r="F226" t="n">
         <v>8</v>
@@ -14422,13 +14422,13 @@
         <v>2812.02181536</v>
       </c>
       <c r="Q226" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R226" t="n">
         <v>2184.32</v>
       </c>
       <c r="S226" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T226" t="n">
         <v>3000</v>
@@ -14448,7 +14448,7 @@
         <v>1.753476338601731</v>
       </c>
       <c r="E227" t="n">
-        <v>24.40122305959177</v>
+        <v>24.36933061131215</v>
       </c>
       <c r="F227" t="n">
         <v>8</v>
@@ -14484,13 +14484,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q227" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R227" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S227" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T227" t="n">
         <v>3000</v>
@@ -14510,7 +14510,7 @@
         <v>4.112175456604231</v>
       </c>
       <c r="E228" t="n">
-        <v>23.95121601827421</v>
+        <v>23.91932356999459</v>
       </c>
       <c r="F228" t="n">
         <v>8</v>
@@ -14546,13 +14546,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q228" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R228" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S228" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T228" t="n">
         <v>3000</v>
@@ -14572,7 +14572,7 @@
         <v>4.503640563549168</v>
       </c>
       <c r="E229" t="n">
-        <v>6.156623313008041</v>
+        <v>6.105134095595598</v>
       </c>
       <c r="F229" t="n">
         <v>8</v>
@@ -14608,13 +14608,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q229" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R229" t="n">
         <v>2184.32</v>
       </c>
       <c r="S229" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T229" t="n">
         <v>3000</v>
@@ -14634,7 +14634,7 @@
         <v>6.305096788968836</v>
       </c>
       <c r="E230" t="n">
-        <v>6.156623313008041</v>
+        <v>6.105134095595598</v>
       </c>
       <c r="F230" t="n">
         <v>8</v>
@@ -14670,13 +14670,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q230" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R230" t="n">
         <v>2184.32</v>
       </c>
       <c r="S230" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T230" t="n">
         <v>3000</v>
@@ -14696,7 +14696,7 @@
         <v>1.370725152201411</v>
       </c>
       <c r="E231" t="n">
-        <v>23.95121601827421</v>
+        <v>23.91932356999459</v>
       </c>
       <c r="F231" t="n">
         <v>8</v>
@@ -14732,13 +14732,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q231" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R231" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S231" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T231" t="n">
         <v>3000</v>
@@ -14758,7 +14758,7 @@
         <v>1.070346349229287</v>
       </c>
       <c r="E232" t="n">
-        <v>9.822343370953043</v>
+        <v>9.769770365481554</v>
       </c>
       <c r="F232" t="n">
         <v>8</v>
@@ -14794,13 +14794,13 @@
         <v>2812.02181536</v>
       </c>
       <c r="Q232" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R232" t="n">
         <v>2184.32</v>
       </c>
       <c r="S232" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T232" t="n">
         <v>3000</v>
@@ -14820,7 +14820,7 @@
         <v>1.801456225419667</v>
       </c>
       <c r="E233" t="n">
-        <v>6.156623313008041</v>
+        <v>6.105134095595598</v>
       </c>
       <c r="F233" t="n">
         <v>8</v>
@@ -14856,13 +14856,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q233" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R233" t="n">
         <v>2184.32</v>
       </c>
       <c r="S233" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T233" t="n">
         <v>3000</v>
@@ -14882,7 +14882,7 @@
         <v>5.260429015805194</v>
       </c>
       <c r="E234" t="n">
-        <v>24.40122305959177</v>
+        <v>24.36933061131215</v>
       </c>
       <c r="F234" t="n">
         <v>8</v>
@@ -14918,13 +14918,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q234" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R234" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S234" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T234" t="n">
         <v>3000</v>
@@ -14944,7 +14944,7 @@
         <v>3.506952677203462</v>
       </c>
       <c r="E235" t="n">
-        <v>24.40122305959177</v>
+        <v>24.36933061131215</v>
       </c>
       <c r="F235" t="n">
         <v>8</v>
@@ -14980,13 +14980,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q235" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R235" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S235" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T235" t="n">
         <v>3000</v>
@@ -15006,7 +15006,7 @@
         <v>2.295226781916666</v>
       </c>
       <c r="E236" t="n">
-        <v>38.25415586667022</v>
+        <v>38.2222634183906</v>
       </c>
       <c r="F236" t="n">
         <v>8</v>
@@ -15042,13 +15042,13 @@
         <v>2812.02181536</v>
       </c>
       <c r="Q236" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R236" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S236" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T236" t="n">
         <v>3000</v>
@@ -15068,7 +15068,7 @@
         <v>2.702184338129501</v>
       </c>
       <c r="E237" t="n">
-        <v>6.156623313008041</v>
+        <v>6.105134095595598</v>
       </c>
       <c r="F237" t="n">
         <v>8</v>
@@ -15104,13 +15104,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q237" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R237" t="n">
         <v>2184.32</v>
       </c>
       <c r="S237" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T237" t="n">
         <v>3000</v>
@@ -15130,7 +15130,7 @@
         <v>12.27433437021212</v>
       </c>
       <c r="E238" t="n">
-        <v>24.40122305959177</v>
+        <v>24.36933061131215</v>
       </c>
       <c r="F238" t="n">
         <v>8</v>
@@ -15166,13 +15166,13 @@
         <v>16304.811096</v>
       </c>
       <c r="Q238" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R238" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S238" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T238" t="n">
         <v>3000</v>
@@ -15192,7 +15192,7 @@
         <v>1.373874021054441</v>
       </c>
       <c r="E239" t="n">
-        <v>6.32673293425486</v>
+        <v>6.275243716842416</v>
       </c>
       <c r="F239" t="n">
         <v>8</v>
@@ -15228,13 +15228,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q239" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R239" t="n">
         <v>2184.32</v>
       </c>
       <c r="S239" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T239" t="n">
         <v>3000</v>
@@ -15254,7 +15254,7 @@
         <v>3.82464076694305</v>
       </c>
       <c r="E240" t="n">
-        <v>6.04412155012036</v>
+        <v>5.992632332707918</v>
       </c>
       <c r="F240" t="n">
         <v>8</v>
@@ -15290,13 +15290,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q240" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R240" t="n">
         <v>2184.32</v>
       </c>
       <c r="S240" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T240" t="n">
         <v>3000</v>
@@ -15316,7 +15316,7 @@
         <v>9.595076065409874</v>
       </c>
       <c r="E241" t="n">
-        <v>23.95121601827421</v>
+        <v>23.91932356999459</v>
       </c>
       <c r="F241" t="n">
         <v>8</v>
@@ -15352,13 +15352,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q241" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R241" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S241" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T241" t="n">
         <v>3000</v>
@@ -15378,7 +15378,7 @@
         <v>1.926505522661574</v>
       </c>
       <c r="E242" t="n">
-        <v>25.08166152910587</v>
+        <v>25.04976908082626</v>
       </c>
       <c r="F242" t="n">
         <v>8</v>
@@ -15414,13 +15414,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q242" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R242" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S242" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T242" t="n">
         <v>3000</v>
@@ -15440,7 +15440,7 @@
         <v>5.779516567984722</v>
       </c>
       <c r="E243" t="n">
-        <v>25.08166152910587</v>
+        <v>25.04976908082626</v>
       </c>
       <c r="F243" t="n">
         <v>8</v>
@@ -15476,13 +15476,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q243" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R243" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S243" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T243" t="n">
         <v>3000</v>
@@ -15502,7 +15502,7 @@
         <v>2.747748042108882</v>
       </c>
       <c r="E244" t="n">
-        <v>6.32673293425486</v>
+        <v>6.275243716842416</v>
       </c>
       <c r="F244" t="n">
         <v>8</v>
@@ -15538,13 +15538,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q244" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R244" t="n">
         <v>2184.32</v>
       </c>
       <c r="S244" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T244" t="n">
         <v>3000</v>
@@ -15564,7 +15564,7 @@
         <v>17.33854970395417</v>
       </c>
       <c r="E245" t="n">
-        <v>25.08166152910587</v>
+        <v>25.04976908082626</v>
       </c>
       <c r="F245" t="n">
         <v>8</v>
@@ -15600,13 +15600,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q245" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R245" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S245" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T245" t="n">
         <v>3000</v>
@@ -15626,7 +15626,7 @@
         <v>6.853625761007053</v>
       </c>
       <c r="E246" t="n">
-        <v>23.95121601827421</v>
+        <v>23.91932356999459</v>
       </c>
       <c r="F246" t="n">
         <v>8</v>
@@ -15662,13 +15662,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q246" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R246" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S246" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T246" t="n">
         <v>3000</v>
@@ -15688,7 +15688,7 @@
         <v>2.731886262102179</v>
       </c>
       <c r="E247" t="n">
-        <v>6.04412155012036</v>
+        <v>5.992632332707918</v>
       </c>
       <c r="F247" t="n">
         <v>8</v>
@@ -15724,13 +15724,13 @@
         <v>9161.013063999999</v>
       </c>
       <c r="Q247" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R247" t="n">
         <v>2184.32</v>
       </c>
       <c r="S247" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T247" t="n">
         <v>3000</v>
@@ -15750,7 +15750,7 @@
         <v>4.121622063163323</v>
       </c>
       <c r="E248" t="n">
-        <v>6.32673293425486</v>
+        <v>6.275243716842416</v>
       </c>
       <c r="F248" t="n">
         <v>8</v>
@@ -15786,13 +15786,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q248" t="n">
-        <v>4027.440000000001</v>
+        <v>80.72</v>
       </c>
       <c r="R248" t="n">
         <v>2184.32</v>
       </c>
       <c r="S248" t="n">
-        <v>1718.8</v>
+        <v>52.48</v>
       </c>
       <c r="T248" t="n">
         <v>3000</v>
@@ -15812,7 +15812,7 @@
         <v>3.853011045323148</v>
       </c>
       <c r="E249" t="n">
-        <v>25.08166152910587</v>
+        <v>25.04976908082626</v>
       </c>
       <c r="F249" t="n">
         <v>8</v>
@@ -15848,13 +15848,13 @@
         <v>27950.93706399999</v>
       </c>
       <c r="Q249" t="n">
-        <v>709.7200000000003</v>
+        <v>14.2</v>
       </c>
       <c r="R249" t="n">
         <v>881.4400000000001</v>
       </c>
       <c r="S249" t="n">
-        <v>200.0200000000002</v>
+        <v>26.36</v>
       </c>
       <c r="T249" t="n">
         <v>3000</v>
@@ -15874,7 +15874,7 @@
         <v>1.639131757261307</v>
       </c>
       <c r="E250" t="n">
-        <v>4.892623232270561</v>
+        <v>4.841134014858117</v>
       </c>
       <c r="F250" t="n">
         <v>10</v>
@@ -15910,13 +15910,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q250" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R250" t="n">
         <v>2730.4</v>
       </c>
       <c r="S250" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T250" t="n">
         <v>3000</v>
@@ -15936,7 +15936,7 @@
         <v>13.48553865863102</v>
       </c>
       <c r="E251" t="n">
-        <v>20.47663428763046</v>
+        <v>20.44474183935084</v>
       </c>
       <c r="F251" t="n">
         <v>10</v>
@@ -15972,13 +15972,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q251" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R251" t="n">
         <v>1101.8</v>
       </c>
       <c r="S251" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T251" t="n">
         <v>3000</v>
@@ -15998,7 +15998,7 @@
         <v>1.092754504840872</v>
       </c>
       <c r="E252" t="n">
-        <v>4.892623232270561</v>
+        <v>4.841134014858117</v>
       </c>
       <c r="F252" t="n">
         <v>10</v>
@@ -16034,13 +16034,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q252" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R252" t="n">
         <v>2730.4</v>
       </c>
       <c r="S252" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T252" t="n">
         <v>3000</v>
@@ -16060,7 +16060,7 @@
         <v>12.3365263698127</v>
       </c>
       <c r="E253" t="n">
-        <v>19.34522285161531</v>
+        <v>19.3133304033357</v>
       </c>
       <c r="F253" t="n">
         <v>10</v>
@@ -16096,13 +16096,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q253" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R253" t="n">
         <v>1101.8</v>
       </c>
       <c r="S253" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T253" t="n">
         <v>3000</v>
@@ -16122,7 +16122,7 @@
         <v>9.632527613307872</v>
       </c>
       <c r="E254" t="n">
-        <v>20.47663428763046</v>
+        <v>20.44474183935084</v>
       </c>
       <c r="F254" t="n">
         <v>10</v>
@@ -16158,13 +16158,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q254" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R254" t="n">
         <v>1101.8</v>
       </c>
       <c r="S254" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T254" t="n">
         <v>3000</v>
@@ -16184,7 +16184,7 @@
         <v>15.78128704741558</v>
       </c>
       <c r="E255" t="n">
-        <v>19.79619581194758</v>
+        <v>19.76430336366796</v>
       </c>
       <c r="F255" t="n">
         <v>10</v>
@@ -16220,13 +16220,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q255" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R255" t="n">
         <v>1101.8</v>
       </c>
       <c r="S255" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T255" t="n">
         <v>3000</v>
@@ -16246,7 +16246,7 @@
         <v>1.926623428612717</v>
       </c>
       <c r="E256" t="n">
-        <v>6.520020641277092</v>
+        <v>6.467447635805602</v>
       </c>
       <c r="F256" t="n">
         <v>10</v>
@@ -16282,13 +16282,13 @@
         <v>3515.0272692</v>
       </c>
       <c r="Q256" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R256" t="n">
         <v>2730.4</v>
       </c>
       <c r="S256" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T256" t="n">
         <v>3000</v>
@@ -16308,7 +16308,7 @@
         <v>4.131408207449998</v>
       </c>
       <c r="E257" t="n">
-        <v>25.31717365666686</v>
+        <v>25.28528120838724</v>
       </c>
       <c r="F257" t="n">
         <v>10</v>
@@ -16344,13 +16344,13 @@
         <v>3515.0272692</v>
       </c>
       <c r="Q257" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R257" t="n">
         <v>1101.8</v>
       </c>
       <c r="S257" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T257" t="n">
         <v>3000</v>
@@ -16370,7 +16370,7 @@
         <v>8.767381693008655</v>
       </c>
       <c r="E258" t="n">
-        <v>19.79619581194758</v>
+        <v>19.76430336366796</v>
       </c>
       <c r="F258" t="n">
         <v>10</v>
@@ -16406,13 +16406,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q258" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R258" t="n">
         <v>1101.8</v>
       </c>
       <c r="S258" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T258" t="n">
         <v>3000</v>
@@ -16432,7 +16432,7 @@
         <v>2.741450304402821</v>
       </c>
       <c r="E259" t="n">
-        <v>19.34522285161531</v>
+        <v>19.3133304033357</v>
       </c>
       <c r="F259" t="n">
         <v>10</v>
@@ -16468,13 +16468,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q259" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R259" t="n">
         <v>1101.8</v>
       </c>
       <c r="S259" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T259" t="n">
         <v>3000</v>
@@ -16494,7 +16494,7 @@
         <v>3.213317494683332</v>
       </c>
       <c r="E260" t="n">
-        <v>25.31717365666686</v>
+        <v>25.28528120838724</v>
       </c>
       <c r="F260" t="n">
         <v>10</v>
@@ -16530,13 +16530,13 @@
         <v>3515.0272692</v>
       </c>
       <c r="Q260" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R260" t="n">
         <v>1101.8</v>
       </c>
       <c r="S260" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T260" t="n">
         <v>3000</v>
@@ -16556,7 +16556,7 @@
         <v>0.9180907127666663</v>
       </c>
       <c r="E261" t="n">
-        <v>25.31717365666686</v>
+        <v>25.28528120838724</v>
       </c>
       <c r="F261" t="n">
         <v>10</v>
@@ -16592,13 +16592,13 @@
         <v>3515.0272692</v>
       </c>
       <c r="Q261" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R261" t="n">
         <v>1101.8</v>
       </c>
       <c r="S261" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T261" t="n">
         <v>3000</v>
@@ -16618,7 +16618,7 @@
         <v>1.377136069149999</v>
       </c>
       <c r="E262" t="n">
-        <v>25.31717365666686</v>
+        <v>25.28528120838724</v>
       </c>
       <c r="F262" t="n">
         <v>10</v>
@@ -16654,13 +16654,13 @@
         <v>3515.0272692</v>
       </c>
       <c r="Q262" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R262" t="n">
         <v>1101.8</v>
       </c>
       <c r="S262" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T262" t="n">
         <v>3000</v>
@@ -16680,7 +16680,7 @@
         <v>1.498484888921002</v>
       </c>
       <c r="E263" t="n">
-        <v>6.520020641277092</v>
+        <v>6.467447635805602</v>
       </c>
       <c r="F263" t="n">
         <v>10</v>
@@ -16716,13 +16716,13 @@
         <v>3515.0272692</v>
       </c>
       <c r="Q263" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R263" t="n">
         <v>2730.4</v>
       </c>
       <c r="S263" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T263" t="n">
         <v>3000</v>
@@ -16742,7 +16742,7 @@
         <v>1.753476338601731</v>
       </c>
       <c r="E264" t="n">
-        <v>19.79619581194758</v>
+        <v>19.76430336366796</v>
       </c>
       <c r="F264" t="n">
         <v>10</v>
@@ -16778,13 +16778,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q264" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R264" t="n">
         <v>1101.8</v>
       </c>
       <c r="S264" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T264" t="n">
         <v>3000</v>
@@ -16804,7 +16804,7 @@
         <v>4.112175456604231</v>
       </c>
       <c r="E265" t="n">
-        <v>19.34522285161531</v>
+        <v>19.3133304033357</v>
       </c>
       <c r="F265" t="n">
         <v>10</v>
@@ -16840,13 +16840,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q265" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R265" t="n">
         <v>1101.8</v>
       </c>
       <c r="S265" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T265" t="n">
         <v>3000</v>
@@ -16866,7 +16866,7 @@
         <v>1.370725152201411</v>
       </c>
       <c r="E266" t="n">
-        <v>19.34522285161531</v>
+        <v>19.3133304033357</v>
       </c>
       <c r="F266" t="n">
         <v>10</v>
@@ -16902,13 +16902,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q266" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R266" t="n">
         <v>1101.8</v>
       </c>
       <c r="S266" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T266" t="n">
         <v>3000</v>
@@ -16928,7 +16928,7 @@
         <v>1.070346349229287</v>
       </c>
       <c r="E267" t="n">
-        <v>6.520020641277092</v>
+        <v>6.467447635805602</v>
       </c>
       <c r="F267" t="n">
         <v>10</v>
@@ -16964,13 +16964,13 @@
         <v>3515.0272692</v>
       </c>
       <c r="Q267" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R267" t="n">
         <v>2730.4</v>
       </c>
       <c r="S267" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T267" t="n">
         <v>3000</v>
@@ -16990,7 +16990,7 @@
         <v>1.801456225419667</v>
       </c>
       <c r="E268" t="n">
-        <v>5.005366474917407</v>
+        <v>4.953877257504964</v>
       </c>
       <c r="F268" t="n">
         <v>10</v>
@@ -17026,13 +17026,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q268" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R268" t="n">
         <v>2730.4</v>
       </c>
       <c r="S268" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T268" t="n">
         <v>3000</v>
@@ -17052,7 +17052,7 @@
         <v>5.260429015805194</v>
       </c>
       <c r="E269" t="n">
-        <v>19.79619581194758</v>
+        <v>19.76430336366796</v>
       </c>
       <c r="F269" t="n">
         <v>10</v>
@@ -17088,13 +17088,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q269" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R269" t="n">
         <v>1101.8</v>
       </c>
       <c r="S269" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T269" t="n">
         <v>3000</v>
@@ -17114,7 +17114,7 @@
         <v>3.506952677203462</v>
       </c>
       <c r="E270" t="n">
-        <v>19.79619581194758</v>
+        <v>19.76430336366796</v>
       </c>
       <c r="F270" t="n">
         <v>10</v>
@@ -17150,13 +17150,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q270" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R270" t="n">
         <v>1101.8</v>
       </c>
       <c r="S270" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T270" t="n">
         <v>3000</v>
@@ -17176,7 +17176,7 @@
         <v>2.295226781916666</v>
       </c>
       <c r="E271" t="n">
-        <v>25.31717365666686</v>
+        <v>25.28528120838724</v>
       </c>
       <c r="F271" t="n">
         <v>10</v>
@@ -17212,13 +17212,13 @@
         <v>3515.0272692</v>
       </c>
       <c r="Q271" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R271" t="n">
         <v>1101.8</v>
       </c>
       <c r="S271" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T271" t="n">
         <v>3000</v>
@@ -17238,7 +17238,7 @@
         <v>2.702184338129501</v>
       </c>
       <c r="E272" t="n">
-        <v>5.005366474917407</v>
+        <v>4.953877257504964</v>
       </c>
       <c r="F272" t="n">
         <v>10</v>
@@ -17274,13 +17274,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q272" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R272" t="n">
         <v>2730.4</v>
       </c>
       <c r="S272" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T272" t="n">
         <v>3000</v>
@@ -17300,7 +17300,7 @@
         <v>12.27433437021212</v>
       </c>
       <c r="E273" t="n">
-        <v>19.79619581194758</v>
+        <v>19.76430336366796</v>
       </c>
       <c r="F273" t="n">
         <v>10</v>
@@ -17336,13 +17336,13 @@
         <v>20381.01387</v>
       </c>
       <c r="Q273" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R273" t="n">
         <v>1101.8</v>
       </c>
       <c r="S273" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T273" t="n">
         <v>3000</v>
@@ -17362,7 +17362,7 @@
         <v>1.373874021054441</v>
       </c>
       <c r="E274" t="n">
-        <v>5.175476097706421</v>
+        <v>5.123986880293978</v>
       </c>
       <c r="F274" t="n">
         <v>10</v>
@@ -17398,13 +17398,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q274" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R274" t="n">
         <v>2730.4</v>
       </c>
       <c r="S274" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T274" t="n">
         <v>3000</v>
@@ -17424,7 +17424,7 @@
         <v>3.82464076694305</v>
       </c>
       <c r="E275" t="n">
-        <v>4.892623232270561</v>
+        <v>4.841134014858117</v>
       </c>
       <c r="F275" t="n">
         <v>10</v>
@@ -17460,13 +17460,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q275" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R275" t="n">
         <v>2730.4</v>
       </c>
       <c r="S275" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T275" t="n">
         <v>3000</v>
@@ -17486,7 +17486,7 @@
         <v>9.595076065409874</v>
       </c>
       <c r="E276" t="n">
-        <v>19.34522285161531</v>
+        <v>19.3133304033357</v>
       </c>
       <c r="F276" t="n">
         <v>10</v>
@@ -17522,13 +17522,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q276" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R276" t="n">
         <v>1101.8</v>
       </c>
       <c r="S276" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T276" t="n">
         <v>3000</v>
@@ -17548,7 +17548,7 @@
         <v>1.926505522661574</v>
       </c>
       <c r="E277" t="n">
-        <v>20.47663428763046</v>
+        <v>20.44474183935084</v>
       </c>
       <c r="F277" t="n">
         <v>10</v>
@@ -17584,13 +17584,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q277" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R277" t="n">
         <v>1101.8</v>
       </c>
       <c r="S277" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T277" t="n">
         <v>3000</v>
@@ -17610,7 +17610,7 @@
         <v>5.779516567984722</v>
       </c>
       <c r="E278" t="n">
-        <v>20.47663428763046</v>
+        <v>20.44474183935084</v>
       </c>
       <c r="F278" t="n">
         <v>10</v>
@@ -17646,13 +17646,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q278" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R278" t="n">
         <v>1101.8</v>
       </c>
       <c r="S278" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T278" t="n">
         <v>3000</v>
@@ -17672,7 +17672,7 @@
         <v>2.747748042108882</v>
       </c>
       <c r="E279" t="n">
-        <v>5.175476097706421</v>
+        <v>5.123986880293978</v>
       </c>
       <c r="F279" t="n">
         <v>10</v>
@@ -17708,13 +17708,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q279" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R279" t="n">
         <v>2730.4</v>
       </c>
       <c r="S279" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T279" t="n">
         <v>3000</v>
@@ -17734,7 +17734,7 @@
         <v>17.33854970395417</v>
       </c>
       <c r="E280" t="n">
-        <v>20.47663428763046</v>
+        <v>20.44474183935084</v>
       </c>
       <c r="F280" t="n">
         <v>10</v>
@@ -17770,13 +17770,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q280" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R280" t="n">
         <v>1101.8</v>
       </c>
       <c r="S280" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T280" t="n">
         <v>3000</v>
@@ -17796,7 +17796,7 @@
         <v>6.853625761007053</v>
       </c>
       <c r="E281" t="n">
-        <v>19.34522285161531</v>
+        <v>19.3133304033357</v>
       </c>
       <c r="F281" t="n">
         <v>10</v>
@@ -17832,13 +17832,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q281" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R281" t="n">
         <v>1101.8</v>
       </c>
       <c r="S281" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T281" t="n">
         <v>3000</v>
@@ -17858,7 +17858,7 @@
         <v>2.731886262102179</v>
       </c>
       <c r="E282" t="n">
-        <v>4.892623232270561</v>
+        <v>4.841134014858117</v>
       </c>
       <c r="F282" t="n">
         <v>10</v>
@@ -17894,13 +17894,13 @@
         <v>11451.26633</v>
       </c>
       <c r="Q282" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R282" t="n">
         <v>2730.4</v>
       </c>
       <c r="S282" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T282" t="n">
         <v>3000</v>
@@ -17920,7 +17920,7 @@
         <v>4.121622063163323</v>
       </c>
       <c r="E283" t="n">
-        <v>5.175476097706421</v>
+        <v>5.123986880293978</v>
       </c>
       <c r="F283" t="n">
         <v>10</v>
@@ -17956,13 +17956,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q283" t="n">
-        <v>5034.300000000001</v>
+        <v>100.9</v>
       </c>
       <c r="R283" t="n">
         <v>2730.4</v>
       </c>
       <c r="S283" t="n">
-        <v>2148.5</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="T283" t="n">
         <v>3000</v>
@@ -17982,7 +17982,7 @@
         <v>3.853011045323148</v>
       </c>
       <c r="E284" t="n">
-        <v>20.47663428763046</v>
+        <v>20.44474183935084</v>
       </c>
       <c r="F284" t="n">
         <v>10</v>
@@ -18018,13 +18018,13 @@
         <v>34938.67132999999</v>
       </c>
       <c r="Q284" t="n">
-        <v>887.1500000000003</v>
+        <v>17.75</v>
       </c>
       <c r="R284" t="n">
         <v>1101.8</v>
       </c>
       <c r="S284" t="n">
-        <v>250.0250000000003</v>
+        <v>32.95</v>
       </c>
       <c r="T284" t="n">
         <v>3000</v>
@@ -18044,7 +18044,7 @@
         <v>1.639131757261307</v>
       </c>
       <c r="E285" t="n">
-        <v>4.125109073078816</v>
+        <v>4.073619855666372</v>
       </c>
       <c r="F285" t="n">
         <v>12</v>
@@ -18080,13 +18080,13 @@
         <v>13741.519596</v>
       </c>
       <c r="Q285" t="n">
-        <v>6041.160000000001</v>
+        <v>121.08</v>
       </c>
       <c r="R285" t="n">
         <v>3276.48</v>
       </c>
       <c r="S285" t="n">
-        <v>2578.2</v>
+        <v>78.72</v>
       </c>
       <c r="T285" t="n">
         <v>3000</v>
@@ -18106,7 +18106,7 @@
         <v>13.48553865863102</v>
       </c>
       <c r="E286" t="n">
-        <v>17.40661612664685</v>
+        <v>17.37472367836723</v>
       </c>
       <c r="F286" t="n">
         <v>12</v>
@@ -18142,13 +18142,13 @@
         <v>41926.40559599999</v>
       </c>
       <c r="Q286" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R286" t="n">
         <v>1322.16</v>
       </c>
       <c r="S286" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T286" t="n">
         <v>3000</v>
@@ -18168,7 +18168,7 @@
         <v>1.092754504840872</v>
       </c>
       <c r="E287" t="n">
-        <v>4.125109073078816</v>
+        <v>4.073619855666372</v>
       </c>
       <c r="F287" t="n">
         <v>12</v>
@@ -18204,13 +18204,13 @@
         <v>13741.519596</v>
       </c>
       <c r="Q287" t="n">
-        <v>6041.160000000001</v>
+        <v>121.08</v>
       </c>
       <c r="R287" t="n">
         <v>3276.48</v>
       </c>
       <c r="S287" t="n">
-        <v>2578.2</v>
+        <v>78.72</v>
       </c>
       <c r="T287" t="n">
         <v>3000</v>
@@ -18230,7 +18230,7 @@
         <v>12.3365263698127</v>
       </c>
       <c r="E288" t="n">
-        <v>16.27516628466141</v>
+        <v>16.2432738363818</v>
       </c>
       <c r="F288" t="n">
         <v>12</v>
@@ -18266,13 +18266,13 @@
         <v>13741.519596</v>
       </c>
       <c r="Q288" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R288" t="n">
         <v>1322.16</v>
       </c>
       <c r="S288" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T288" t="n">
         <v>3000</v>
@@ -18292,7 +18292,7 @@
         <v>9.632527613307872</v>
       </c>
       <c r="E289" t="n">
-        <v>17.40661612664685</v>
+        <v>17.37472367836723</v>
       </c>
       <c r="F289" t="n">
         <v>12</v>
@@ -18328,13 +18328,13 @@
         <v>41926.40559599999</v>
       </c>
       <c r="Q289" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R289" t="n">
         <v>1322.16</v>
       </c>
       <c r="S289" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T289" t="n">
         <v>3000</v>
@@ -18354,7 +18354,7 @@
         <v>15.78128704741558</v>
       </c>
       <c r="E290" t="n">
-        <v>16.72617765095173</v>
+        <v>16.69428520267211</v>
       </c>
       <c r="F290" t="n">
         <v>12</v>
@@ -18390,13 +18390,13 @@
         <v>24457.216644</v>
       </c>
       <c r="Q290" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R290" t="n">
         <v>1322.16</v>
       </c>
       <c r="S290" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T290" t="n">
         <v>3000</v>
@@ -18416,7 +18416,7 @@
         <v>1.926623428612717</v>
       </c>
       <c r="E291" t="n">
-        <v>4.833028907372994</v>
+        <v>4.780455901901506</v>
       </c>
       <c r="F291" t="n">
         <v>12</v>
@@ -18452,13 +18452,13 @@
         <v>4218.03272304</v>
       </c>
       <c r="Q291" t="n">
-        <v>6041.160000000001</v>
+        <v>121.08</v>
       </c>
       <c r="R291" t="n">
         <v>3276.48</v>
       </c>
       <c r="S291" t="n">
-        <v>2578.2</v>
+        <v>78.72</v>
       </c>
       <c r="T291" t="n">
         <v>3000</v>
@@ -18478,7 +18478,7 @@
         <v>4.131408207449998</v>
       </c>
       <c r="E292" t="n">
-        <v>18.70831563869791</v>
+        <v>18.67642319041829</v>
       </c>
       <c r="F292" t="n">
         <v>12</v>
@@ -18514,13 +18514,13 @@
         <v>4218.03272304</v>
       </c>
       <c r="Q292" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R292" t="n">
         <v>1322.16</v>
       </c>
       <c r="S292" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T292" t="n">
         <v>3000</v>
@@ -18540,7 +18540,7 @@
         <v>8.767381693008655</v>
       </c>
       <c r="E293" t="n">
-        <v>16.72617765095173</v>
+        <v>16.69428520267211</v>
       </c>
       <c r="F293" t="n">
         <v>12</v>
@@ -18576,13 +18576,13 @@
         <v>24457.216644</v>
       </c>
       <c r="Q293" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R293" t="n">
         <v>1322.16</v>
       </c>
       <c r="S293" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T293" t="n">
         <v>3000</v>
@@ -18602,7 +18602,7 @@
         <v>2.741450304402821</v>
       </c>
       <c r="E294" t="n">
-        <v>16.27516628466141</v>
+        <v>16.2432738363818</v>
       </c>
       <c r="F294" t="n">
         <v>12</v>
@@ -18638,13 +18638,13 @@
         <v>13741.519596</v>
       </c>
       <c r="Q294" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R294" t="n">
         <v>1322.16</v>
       </c>
       <c r="S294" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T294" t="n">
         <v>3000</v>
@@ -18664,7 +18664,7 @@
         <v>3.213317494683332</v>
       </c>
       <c r="E295" t="n">
-        <v>18.70831563869791</v>
+        <v>18.67642319041829</v>
       </c>
       <c r="F295" t="n">
         <v>12</v>
@@ -18700,13 +18700,13 @@
         <v>4218.03272304</v>
       </c>
       <c r="Q295" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R295" t="n">
         <v>1322.16</v>
       </c>
       <c r="S295" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T295" t="n">
         <v>3000</v>
@@ -18726,7 +18726,7 @@
         <v>0.9180907127666663</v>
       </c>
       <c r="E296" t="n">
-        <v>18.70831563869791</v>
+        <v>18.67642319041829</v>
       </c>
       <c r="F296" t="n">
         <v>12</v>
@@ -18762,13 +18762,13 @@
         <v>4218.03272304</v>
       </c>
       <c r="Q296" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R296" t="n">
         <v>1322.16</v>
       </c>
       <c r="S296" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T296" t="n">
         <v>3000</v>
@@ -18788,7 +18788,7 @@
         <v>1.377136069149999</v>
       </c>
       <c r="E297" t="n">
-        <v>18.70831563869791</v>
+        <v>18.67642319041829</v>
       </c>
       <c r="F297" t="n">
         <v>12</v>
@@ -18824,13 +18824,13 @@
         <v>4218.03272304</v>
       </c>
       <c r="Q297" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R297" t="n">
         <v>1322.16</v>
       </c>
       <c r="S297" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T297" t="n">
         <v>3000</v>
@@ -18850,7 +18850,7 @@
         <v>1.498484888921002</v>
       </c>
       <c r="E298" t="n">
-        <v>4.833028907372994</v>
+        <v>4.780455901901506</v>
       </c>
       <c r="F298" t="n">
         <v>12</v>
@@ -18886,13 +18886,13 @@
         <v>4218.03272304</v>
       </c>
       <c r="Q298" t="n">
-        <v>6041.160000000001</v>
+        <v>121.08</v>
       </c>
       <c r="R298" t="n">
         <v>3276.48</v>
       </c>
       <c r="S298" t="n">
-        <v>2578.2</v>
+        <v>78.72</v>
       </c>
       <c r="T298" t="n">
         <v>3000</v>
@@ -18912,7 +18912,7 @@
         <v>1.753476338601731</v>
       </c>
       <c r="E299" t="n">
-        <v>16.72617765095173</v>
+        <v>16.69428520267211</v>
       </c>
       <c r="F299" t="n">
         <v>12</v>
@@ -18948,13 +18948,13 @@
         <v>24457.216644</v>
       </c>
       <c r="Q299" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R299" t="n">
         <v>1322.16</v>
       </c>
       <c r="S299" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T299" t="n">
         <v>3000</v>
@@ -18974,7 +18974,7 @@
         <v>4.112175456604231</v>
       </c>
       <c r="E300" t="n">
-        <v>16.27516628466141</v>
+        <v>16.2432738363818</v>
       </c>
       <c r="F300" t="n">
         <v>12</v>
@@ -19010,13 +19010,13 @@
         <v>13741.519596</v>
       </c>
       <c r="Q300" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R300" t="n">
         <v>1322.16</v>
       </c>
       <c r="S300" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T300" t="n">
         <v>3000</v>
@@ -19036,7 +19036,7 @@
         <v>1.370725152201411</v>
       </c>
       <c r="E301" t="n">
-        <v>16.27516628466141</v>
+        <v>16.2432738363818</v>
       </c>
       <c r="F301" t="n">
         <v>12</v>
@@ -19072,13 +19072,13 @@
         <v>13741.519596</v>
       </c>
       <c r="Q301" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R301" t="n">
         <v>1322.16</v>
       </c>
       <c r="S301" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T301" t="n">
         <v>3000</v>
@@ -19098,7 +19098,7 @@
         <v>1.070346349229287</v>
       </c>
       <c r="E302" t="n">
-        <v>4.833028907372994</v>
+        <v>4.780455901901506</v>
       </c>
       <c r="F302" t="n">
         <v>12</v>
@@ -19134,13 +19134,13 @@
         <v>4218.03272304</v>
       </c>
       <c r="Q302" t="n">
-        <v>6041.160000000001</v>
+        <v>121.08</v>
       </c>
       <c r="R302" t="n">
         <v>3276.48</v>
       </c>
       <c r="S302" t="n">
-        <v>2578.2</v>
+        <v>78.72</v>
       </c>
       <c r="T302" t="n">
         <v>3000</v>
@@ -19160,7 +19160,7 @@
         <v>1.801456225419667</v>
       </c>
       <c r="E303" t="n">
-        <v>4.237861917215394</v>
+        <v>4.186372699802951</v>
       </c>
       <c r="F303" t="n">
         <v>12</v>
@@ -19196,13 +19196,13 @@
         <v>24457.216644</v>
       </c>
       <c r="Q303" t="n">
-        <v>6041.160000000001</v>
+        <v>121.08</v>
       </c>
       <c r="R303" t="n">
         <v>3276.48</v>
       </c>
       <c r="S303" t="n">
-        <v>2578.2</v>
+        <v>78.72</v>
       </c>
       <c r="T303" t="n">
         <v>3000</v>
@@ -19222,7 +19222,7 @@
         <v>5.260429015805194</v>
       </c>
       <c r="E304" t="n">
-        <v>16.72617765095173</v>
+        <v>16.69428520267211</v>
       </c>
       <c r="F304" t="n">
         <v>12</v>
@@ -19258,13 +19258,13 @@
         <v>24457.216644</v>
       </c>
       <c r="Q304" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R304" t="n">
         <v>1322.16</v>
       </c>
       <c r="S304" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T304" t="n">
         <v>3000</v>
@@ -19284,7 +19284,7 @@
         <v>3.506952677203462</v>
       </c>
       <c r="E305" t="n">
-        <v>16.72617765095173</v>
+        <v>16.69428520267211</v>
       </c>
       <c r="F305" t="n">
         <v>12</v>
@@ -19320,13 +19320,13 @@
         <v>24457.216644</v>
       </c>
       <c r="Q305" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R305" t="n">
         <v>1322.16</v>
       </c>
       <c r="S305" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T305" t="n">
         <v>3000</v>
@@ -19346,7 +19346,7 @@
         <v>2.295226781916666</v>
       </c>
       <c r="E306" t="n">
-        <v>18.70831563869791</v>
+        <v>18.67642319041829</v>
       </c>
       <c r="F306" t="n">
         <v>12</v>
@@ -19382,13 +19382,13 @@
         <v>4218.03272304</v>
       </c>
       <c r="Q306" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R306" t="n">
         <v>1322.16</v>
       </c>
       <c r="S306" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T306" t="n">
         <v>3000</v>
@@ -19408,7 +19408,7 @@
         <v>2.702184338129501</v>
       </c>
       <c r="E307" t="n">
-        <v>4.237861917215394</v>
+        <v>4.186372699802951</v>
       </c>
       <c r="F307" t="n">
         <v>12</v>
@@ -19444,13 +19444,13 @@
         <v>24457.216644</v>
       </c>
       <c r="Q307" t="n">
-        <v>6041.160000000001</v>
+        <v>121.08</v>
       </c>
       <c r="R307" t="n">
         <v>3276.48</v>
       </c>
       <c r="S307" t="n">
-        <v>2578.2</v>
+        <v>78.72</v>
       </c>
       <c r="T307" t="n">
         <v>3000</v>
@@ -19470,7 +19470,7 @@
         <v>12.27433437021212</v>
       </c>
       <c r="E308" t="n">
-        <v>16.72617765095173</v>
+        <v>16.69428520267211</v>
       </c>
       <c r="F308" t="n">
         <v>12</v>
@@ -19506,13 +19506,13 @@
         <v>24457.216644</v>
       </c>
       <c r="Q308" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R308" t="n">
         <v>1322.16</v>
       </c>
       <c r="S308" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T308" t="n">
         <v>3000</v>
@@ -19532,7 +19532,7 @@
         <v>1.373874021054441</v>
       </c>
       <c r="E309" t="n">
-        <v>4.407971540007465</v>
+        <v>4.356482322595022</v>
       </c>
       <c r="F309" t="n">
         <v>12</v>
@@ -19568,13 +19568,13 @@
         <v>41926.40559599999</v>
       </c>
       <c r="Q309" t="n">
-        <v>6041.160000000001</v>
+        <v>121.08</v>
       </c>
       <c r="R309" t="n">
         <v>3276.48</v>
       </c>
       <c r="S309" t="n">
-        <v>2578.2</v>
+        <v>78.72</v>
       </c>
       <c r="T309" t="n">
         <v>3000</v>
@@ -19594,7 +19594,7 @@
         <v>9.595076065409874</v>
       </c>
       <c r="E310" t="n">
-        <v>16.27516628466141</v>
+        <v>16.2432738363818</v>
       </c>
       <c r="F310" t="n">
         <v>12</v>
@@ -19630,13 +19630,13 @@
         <v>13741.519596</v>
       </c>
       <c r="Q310" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R310" t="n">
         <v>1322.16</v>
       </c>
       <c r="S310" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T310" t="n">
         <v>3000</v>
@@ -19656,7 +19656,7 @@
         <v>1.926505522661574</v>
       </c>
       <c r="E311" t="n">
-        <v>17.40661612664685</v>
+        <v>17.37472367836723</v>
       </c>
       <c r="F311" t="n">
         <v>12</v>
@@ -19692,13 +19692,13 @@
         <v>41926.40559599999</v>
       </c>
       <c r="Q311" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R311" t="n">
         <v>1322.16</v>
       </c>
       <c r="S311" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T311" t="n">
         <v>3000</v>
@@ -19718,7 +19718,7 @@
         <v>5.779516567984722</v>
       </c>
       <c r="E312" t="n">
-        <v>17.40661612664685</v>
+        <v>17.37472367836723</v>
       </c>
       <c r="F312" t="n">
         <v>12</v>
@@ -19754,13 +19754,13 @@
         <v>41926.40559599999</v>
       </c>
       <c r="Q312" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R312" t="n">
         <v>1322.16</v>
       </c>
       <c r="S312" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T312" t="n">
         <v>3000</v>
@@ -19780,7 +19780,7 @@
         <v>2.747748042108882</v>
       </c>
       <c r="E313" t="n">
-        <v>4.407971540007465</v>
+        <v>4.356482322595022</v>
       </c>
       <c r="F313" t="n">
         <v>12</v>
@@ -19816,13 +19816,13 @@
         <v>41926.40559599999</v>
       </c>
       <c r="Q313" t="n">
-        <v>6041.160000000001</v>
+        <v>121.08</v>
       </c>
       <c r="R313" t="n">
         <v>3276.48</v>
       </c>
       <c r="S313" t="n">
-        <v>2578.2</v>
+        <v>78.72</v>
       </c>
       <c r="T313" t="n">
         <v>3000</v>
@@ -19842,7 +19842,7 @@
         <v>17.33854970395417</v>
       </c>
       <c r="E314" t="n">
-        <v>17.40661612664685</v>
+        <v>17.37472367836723</v>
       </c>
       <c r="F314" t="n">
         <v>12</v>
@@ -19878,13 +19878,13 @@
         <v>41926.40559599999</v>
       </c>
       <c r="Q314" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R314" t="n">
         <v>1322.16</v>
       </c>
       <c r="S314" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T314" t="n">
         <v>3000</v>
@@ -19904,7 +19904,7 @@
         <v>6.853625761007053</v>
       </c>
       <c r="E315" t="n">
-        <v>16.27516628466141</v>
+        <v>16.2432738363818</v>
       </c>
       <c r="F315" t="n">
         <v>12</v>
@@ -19940,13 +19940,13 @@
         <v>13741.519596</v>
       </c>
       <c r="Q315" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R315" t="n">
         <v>1322.16</v>
       </c>
       <c r="S315" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T315" t="n">
         <v>3000</v>
@@ -19966,7 +19966,7 @@
         <v>2.731886262102179</v>
       </c>
       <c r="E316" t="n">
-        <v>4.125109073078816</v>
+        <v>4.073619855666372</v>
       </c>
       <c r="F316" t="n">
         <v>12</v>
@@ -20002,13 +20002,13 @@
         <v>13741.519596</v>
       </c>
       <c r="Q316" t="n">
-        <v>6041.160000000001</v>
+        <v>121.08</v>
       </c>
       <c r="R316" t="n">
         <v>3276.48</v>
       </c>
       <c r="S316" t="n">
-        <v>2578.2</v>
+        <v>78.72</v>
       </c>
       <c r="T316" t="n">
         <v>3000</v>
@@ -20028,7 +20028,7 @@
         <v>3.853011045323148</v>
       </c>
       <c r="E317" t="n">
-        <v>17.40661612664685</v>
+        <v>17.37472367836723</v>
       </c>
       <c r="F317" t="n">
         <v>12</v>
@@ -20064,13 +20064,13 @@
         <v>41926.40559599999</v>
       </c>
       <c r="Q317" t="n">
-        <v>1064.58</v>
+        <v>21.3</v>
       </c>
       <c r="R317" t="n">
         <v>1322.16</v>
       </c>
       <c r="S317" t="n">
-        <v>300.0300000000003</v>
+        <v>39.54</v>
       </c>
       <c r="T317" t="n">
         <v>3000</v>
